--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -11,7 +11,8 @@
     <sheet name="候選B_blind_spot" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="universe在TWSE排名" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="TWSE前100" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="門檻說明" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OTC轉上市觀察" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="門檻說明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1271,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,6 +1296,11 @@
           <t>比重%</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>市值億</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1313,6 +1319,9 @@
       <c r="D2" t="n">
         <v>41.992</v>
       </c>
+      <c r="E2" t="n">
+        <v>650900</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1331,6 +1340,9 @@
       <c r="D3" t="n">
         <v>4.7532</v>
       </c>
+      <c r="E3" t="n">
+        <v>73677</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1349,6 +1361,9 @@
       <c r="D4" t="n">
         <v>4.3669</v>
       </c>
+      <c r="E4" t="n">
+        <v>67689</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1367,6 +1382,9 @@
       <c r="D5" t="n">
         <v>2.7827</v>
       </c>
+      <c r="E5" t="n">
+        <v>43133</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1385,6 +1403,9 @@
       <c r="D6" t="n">
         <v>1.8741</v>
       </c>
+      <c r="E6" t="n">
+        <v>29050</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1403,6 +1424,9 @@
       <c r="D7" t="n">
         <v>1.2615</v>
       </c>
+      <c r="E7" t="n">
+        <v>19554</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1445,9 @@
       <c r="D8" t="n">
         <v>1.2498</v>
       </c>
+      <c r="E8" t="n">
+        <v>19373</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1439,6 +1466,9 @@
       <c r="D9" t="n">
         <v>1.1429</v>
       </c>
+      <c r="E9" t="n">
+        <v>17716</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1457,6 +1487,9 @@
       <c r="D10" t="n">
         <v>1.0594</v>
       </c>
+      <c r="E10" t="n">
+        <v>16421</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1475,6 +1508,9 @@
       <c r="D11" t="n">
         <v>1.0519</v>
       </c>
+      <c r="E11" t="n">
+        <v>16305</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1493,6 +1529,9 @@
       <c r="D12" t="n">
         <v>1.0219</v>
       </c>
+      <c r="E12" t="n">
+        <v>15840</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1511,6 +1550,9 @@
       <c r="D13" t="n">
         <v>0.9375</v>
       </c>
+      <c r="E13" t="n">
+        <v>14532</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1529,6 +1571,9 @@
       <c r="D14" t="n">
         <v>0.9004</v>
       </c>
+      <c r="E14" t="n">
+        <v>13957</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1547,6 +1592,9 @@
       <c r="D15" t="n">
         <v>0.8643999999999999</v>
       </c>
+      <c r="E15" t="n">
+        <v>13399</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1565,6 +1613,9 @@
       <c r="D16" t="n">
         <v>0.8186</v>
       </c>
+      <c r="E16" t="n">
+        <v>12689</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1583,6 +1634,9 @@
       <c r="D17" t="n">
         <v>0.7393</v>
       </c>
+      <c r="E17" t="n">
+        <v>11460</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1601,6 +1655,9 @@
       <c r="D18" t="n">
         <v>0.7368</v>
       </c>
+      <c r="E18" t="n">
+        <v>11421</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1619,6 +1676,9 @@
       <c r="D19" t="n">
         <v>0.7308</v>
       </c>
+      <c r="E19" t="n">
+        <v>11328</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1637,6 +1697,9 @@
       <c r="D20" t="n">
         <v>0.7186</v>
       </c>
+      <c r="E20" t="n">
+        <v>11139</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1655,6 +1718,9 @@
       <c r="D21" t="n">
         <v>0.6958</v>
       </c>
+      <c r="E21" t="n">
+        <v>10785</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1673,6 +1739,9 @@
       <c r="D22" t="n">
         <v>0.5463</v>
       </c>
+      <c r="E22" t="n">
+        <v>8468</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1691,6 +1760,9 @@
       <c r="D23" t="n">
         <v>0.535</v>
       </c>
+      <c r="E23" t="n">
+        <v>8293</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1709,6 +1781,9 @@
       <c r="D24" t="n">
         <v>0.4889</v>
       </c>
+      <c r="E24" t="n">
+        <v>7578</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1727,6 +1802,9 @@
       <c r="D25" t="n">
         <v>0.4634</v>
       </c>
+      <c r="E25" t="n">
+        <v>7183</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1745,6 +1823,9 @@
       <c r="D26" t="n">
         <v>0.4303</v>
       </c>
+      <c r="E26" t="n">
+        <v>6670</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1763,6 +1844,9 @@
       <c r="D27" t="n">
         <v>0.408</v>
       </c>
+      <c r="E27" t="n">
+        <v>6324</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1781,6 +1865,9 @@
       <c r="D28" t="n">
         <v>0.3992</v>
       </c>
+      <c r="E28" t="n">
+        <v>6188</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1799,6 +1886,9 @@
       <c r="D29" t="n">
         <v>0.3887</v>
       </c>
+      <c r="E29" t="n">
+        <v>6025</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1817,6 +1907,9 @@
       <c r="D30" t="n">
         <v>0.3791</v>
       </c>
+      <c r="E30" t="n">
+        <v>5876</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1835,6 +1928,9 @@
       <c r="D31" t="n">
         <v>0.3768</v>
       </c>
+      <c r="E31" t="n">
+        <v>5841</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1853,6 +1949,9 @@
       <c r="D32" t="n">
         <v>0.3736</v>
       </c>
+      <c r="E32" t="n">
+        <v>5791</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1871,6 +1970,9 @@
       <c r="D33" t="n">
         <v>0.3577</v>
       </c>
+      <c r="E33" t="n">
+        <v>5545</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1889,6 +1991,9 @@
       <c r="D34" t="n">
         <v>0.3466</v>
       </c>
+      <c r="E34" t="n">
+        <v>5372</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1907,6 +2012,9 @@
       <c r="D35" t="n">
         <v>0.3442</v>
       </c>
+      <c r="E35" t="n">
+        <v>5335</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1925,6 +2033,9 @@
       <c r="D36" t="n">
         <v>0.3367</v>
       </c>
+      <c r="E36" t="n">
+        <v>5219</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1943,6 +2054,9 @@
       <c r="D37" t="n">
         <v>0.3319</v>
       </c>
+      <c r="E37" t="n">
+        <v>5145</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1961,6 +2075,9 @@
       <c r="D38" t="n">
         <v>0.3226</v>
       </c>
+      <c r="E38" t="n">
+        <v>5000</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1979,6 +2096,9 @@
       <c r="D39" t="n">
         <v>0.3171</v>
       </c>
+      <c r="E39" t="n">
+        <v>4915</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1997,6 +2117,9 @@
       <c r="D40" t="n">
         <v>0.2989</v>
       </c>
+      <c r="E40" t="n">
+        <v>4633</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2015,6 +2138,9 @@
       <c r="D41" t="n">
         <v>0.2947</v>
       </c>
+      <c r="E41" t="n">
+        <v>4568</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2033,6 +2159,9 @@
       <c r="D42" t="n">
         <v>0.2919</v>
       </c>
+      <c r="E42" t="n">
+        <v>4525</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2051,6 +2180,9 @@
       <c r="D43" t="n">
         <v>0.2854</v>
       </c>
+      <c r="E43" t="n">
+        <v>4424</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2069,6 +2201,9 @@
       <c r="D44" t="n">
         <v>0.2805</v>
       </c>
+      <c r="E44" t="n">
+        <v>4348</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2087,6 +2222,9 @@
       <c r="D45" t="n">
         <v>0.2802</v>
       </c>
+      <c r="E45" t="n">
+        <v>4343</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2105,6 +2243,9 @@
       <c r="D46" t="n">
         <v>0.2797</v>
       </c>
+      <c r="E46" t="n">
+        <v>4336</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2123,6 +2264,9 @@
       <c r="D47" t="n">
         <v>0.2762</v>
       </c>
+      <c r="E47" t="n">
+        <v>4281</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2141,6 +2285,9 @@
       <c r="D48" t="n">
         <v>0.2714</v>
       </c>
+      <c r="E48" t="n">
+        <v>4207</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2159,6 +2306,9 @@
       <c r="D49" t="n">
         <v>0.2641</v>
       </c>
+      <c r="E49" t="n">
+        <v>4094</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2177,6 +2327,9 @@
       <c r="D50" t="n">
         <v>0.2626</v>
       </c>
+      <c r="E50" t="n">
+        <v>4070</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2195,6 +2348,9 @@
       <c r="D51" t="n">
         <v>0.2577</v>
       </c>
+      <c r="E51" t="n">
+        <v>3994</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2213,6 +2369,9 @@
       <c r="D52" t="n">
         <v>0.251</v>
       </c>
+      <c r="E52" t="n">
+        <v>3891</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2231,6 +2390,9 @@
       <c r="D53" t="n">
         <v>0.2464</v>
       </c>
+      <c r="E53" t="n">
+        <v>3819</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2249,6 +2411,9 @@
       <c r="D54" t="n">
         <v>0.2429</v>
       </c>
+      <c r="E54" t="n">
+        <v>3765</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2267,6 +2432,9 @@
       <c r="D55" t="n">
         <v>0.2408</v>
       </c>
+      <c r="E55" t="n">
+        <v>3733</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2285,6 +2453,9 @@
       <c r="D56" t="n">
         <v>0.2331</v>
       </c>
+      <c r="E56" t="n">
+        <v>3613</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2303,6 +2474,9 @@
       <c r="D57" t="n">
         <v>0.2285</v>
       </c>
+      <c r="E57" t="n">
+        <v>3542</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2321,6 +2495,9 @@
       <c r="D58" t="n">
         <v>0.2211</v>
       </c>
+      <c r="E58" t="n">
+        <v>3427</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2339,6 +2516,9 @@
       <c r="D59" t="n">
         <v>0.2147</v>
       </c>
+      <c r="E59" t="n">
+        <v>3328</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2357,6 +2537,9 @@
       <c r="D60" t="n">
         <v>0.2077</v>
       </c>
+      <c r="E60" t="n">
+        <v>3219</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2375,6 +2558,9 @@
       <c r="D61" t="n">
         <v>0.2066</v>
       </c>
+      <c r="E61" t="n">
+        <v>3202</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2393,6 +2579,9 @@
       <c r="D62" t="n">
         <v>0.2056</v>
       </c>
+      <c r="E62" t="n">
+        <v>3187</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2411,6 +2600,9 @@
       <c r="D63" t="n">
         <v>0.2051</v>
       </c>
+      <c r="E63" t="n">
+        <v>3179</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2429,6 +2621,9 @@
       <c r="D64" t="n">
         <v>0.2011</v>
       </c>
+      <c r="E64" t="n">
+        <v>3117</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2447,6 +2642,9 @@
       <c r="D65" t="n">
         <v>0.1996</v>
       </c>
+      <c r="E65" t="n">
+        <v>3094</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2465,6 +2663,9 @@
       <c r="D66" t="n">
         <v>0.1978</v>
       </c>
+      <c r="E66" t="n">
+        <v>3066</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2483,6 +2684,9 @@
       <c r="D67" t="n">
         <v>0.1925</v>
       </c>
+      <c r="E67" t="n">
+        <v>2984</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2501,6 +2705,9 @@
       <c r="D68" t="n">
         <v>0.1898</v>
       </c>
+      <c r="E68" t="n">
+        <v>2942</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2519,6 +2726,9 @@
       <c r="D69" t="n">
         <v>0.1883</v>
       </c>
+      <c r="E69" t="n">
+        <v>2919</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2537,6 +2747,9 @@
       <c r="D70" t="n">
         <v>0.185</v>
       </c>
+      <c r="E70" t="n">
+        <v>2868</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2555,6 +2768,9 @@
       <c r="D71" t="n">
         <v>0.1732</v>
       </c>
+      <c r="E71" t="n">
+        <v>2685</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2573,6 +2789,9 @@
       <c r="D72" t="n">
         <v>0.1704</v>
       </c>
+      <c r="E72" t="n">
+        <v>2641</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2591,6 +2810,9 @@
       <c r="D73" t="n">
         <v>0.1638</v>
       </c>
+      <c r="E73" t="n">
+        <v>2539</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2609,6 +2831,9 @@
       <c r="D74" t="n">
         <v>0.1632</v>
       </c>
+      <c r="E74" t="n">
+        <v>2530</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2627,6 +2852,9 @@
       <c r="D75" t="n">
         <v>0.1605</v>
       </c>
+      <c r="E75" t="n">
+        <v>2488</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2645,6 +2873,9 @@
       <c r="D76" t="n">
         <v>0.1582</v>
       </c>
+      <c r="E76" t="n">
+        <v>2452</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2663,6 +2894,9 @@
       <c r="D77" t="n">
         <v>0.153</v>
       </c>
+      <c r="E77" t="n">
+        <v>2372</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2681,6 +2915,9 @@
       <c r="D78" t="n">
         <v>0.1514</v>
       </c>
+      <c r="E78" t="n">
+        <v>2347</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2699,6 +2936,9 @@
       <c r="D79" t="n">
         <v>0.1438</v>
       </c>
+      <c r="E79" t="n">
+        <v>2229</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2717,6 +2957,9 @@
       <c r="D80" t="n">
         <v>0.1357</v>
       </c>
+      <c r="E80" t="n">
+        <v>2103</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2735,6 +2978,9 @@
       <c r="D81" t="n">
         <v>0.1339</v>
       </c>
+      <c r="E81" t="n">
+        <v>2076</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2753,6 +2999,9 @@
       <c r="D82" t="n">
         <v>0.1331</v>
       </c>
+      <c r="E82" t="n">
+        <v>2063</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2771,6 +3020,9 @@
       <c r="D83" t="n">
         <v>0.1329</v>
       </c>
+      <c r="E83" t="n">
+        <v>2060</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2789,6 +3041,9 @@
       <c r="D84" t="n">
         <v>0.1316</v>
       </c>
+      <c r="E84" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2807,6 +3062,9 @@
       <c r="D85" t="n">
         <v>0.127</v>
       </c>
+      <c r="E85" t="n">
+        <v>1969</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2825,6 +3083,9 @@
       <c r="D86" t="n">
         <v>0.1265</v>
       </c>
+      <c r="E86" t="n">
+        <v>1961</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2843,6 +3104,9 @@
       <c r="D87" t="n">
         <v>0.1265</v>
       </c>
+      <c r="E87" t="n">
+        <v>1961</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2861,6 +3125,9 @@
       <c r="D88" t="n">
         <v>0.1262</v>
       </c>
+      <c r="E88" t="n">
+        <v>1956</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2879,6 +3146,9 @@
       <c r="D89" t="n">
         <v>0.1226</v>
       </c>
+      <c r="E89" t="n">
+        <v>1900</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2897,6 +3167,9 @@
       <c r="D90" t="n">
         <v>0.1194</v>
       </c>
+      <c r="E90" t="n">
+        <v>1851</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2915,6 +3188,9 @@
       <c r="D91" t="n">
         <v>0.1181</v>
       </c>
+      <c r="E91" t="n">
+        <v>1831</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2933,6 +3209,9 @@
       <c r="D92" t="n">
         <v>0.1181</v>
       </c>
+      <c r="E92" t="n">
+        <v>1831</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2951,6 +3230,9 @@
       <c r="D93" t="n">
         <v>0.1176</v>
       </c>
+      <c r="E93" t="n">
+        <v>1823</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2969,6 +3251,9 @@
       <c r="D94" t="n">
         <v>0.1151</v>
       </c>
+      <c r="E94" t="n">
+        <v>1784</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2987,6 +3272,9 @@
       <c r="D95" t="n">
         <v>0.1112</v>
       </c>
+      <c r="E95" t="n">
+        <v>1724</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3005,6 +3293,9 @@
       <c r="D96" t="n">
         <v>0.1086</v>
       </c>
+      <c r="E96" t="n">
+        <v>1683</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3023,6 +3314,9 @@
       <c r="D97" t="n">
         <v>0.1076</v>
       </c>
+      <c r="E97" t="n">
+        <v>1668</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3041,6 +3335,9 @@
       <c r="D98" t="n">
         <v>0.1061</v>
       </c>
+      <c r="E98" t="n">
+        <v>1645</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3059,6 +3356,9 @@
       <c r="D99" t="n">
         <v>0.1001</v>
       </c>
+      <c r="E99" t="n">
+        <v>1552</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3077,6 +3377,9 @@
       <c r="D100" t="n">
         <v>0.099</v>
       </c>
+      <c r="E100" t="n">
+        <v>1535</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3094,6 +3397,9 @@
       </c>
       <c r="D101" t="n">
         <v>0.0985</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1527</v>
       </c>
     </row>
   </sheetData>
@@ -3107,6 +3413,340 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>OTC排名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>市值億</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>轉上市定位</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>在我們PICKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6995.4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6545.1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5372.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5055.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4828.9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>世界先進</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3482.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>力旺電子</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2378.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8069</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>元太</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2262.5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2213</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>鈊象電子</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2141.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2114</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>頎邦科技</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1921</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -11,8 +11,10 @@
     <sheet name="候選B_blind_spot" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="universe在TWSE排名" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="TWSE前100" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="OTC轉上市觀察" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="門檻說明" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="富櫃50候選B_blind" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OTC前100" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="OTC轉上市觀察" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="門檻說明" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3413,7 +3415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3439,302 +3441,929 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>轉上市定位</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>在我們PICKS</t>
+          <t>建議</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6995.4</v>
+        <v>359.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>旺矽科技</t>
+          <t>德宏工業</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6545.1</v>
+        <v>354.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5372.4</v>
+        <v>353.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5055.4</v>
+        <v>343.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>中國探針</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4828.9</v>
+        <v>320</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>元大期</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3482.7</v>
+        <v>320</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>力旺電子</t>
+          <t>宏捷科技</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2378.8</v>
+        <v>313.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2262.5</v>
+        <v>303.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>中強光電</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2213</v>
+        <v>299.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>鈊象電子</t>
+          <t>高技企業</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2141.7</v>
+        <v>298.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>鈺創科技</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2114</v>
+        <v>298.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>東捷科技</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1921</v>
+        <v>288.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>63</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>晟德</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>64</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>朋億*</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>286.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>65</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>先進光</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>66</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6138</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>茂達電子</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>273</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>67</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>是方</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>265.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>68</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>262</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>69</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8027</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>鈦昇</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>260.7</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>70</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6903</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>巨漢</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>254</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>71</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>台星科</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>247.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>72</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8155</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>博智</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>239.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>73</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3675</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>德微</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>74</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4743</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>合一</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>75</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>8042</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>金山電子</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>230.6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>76</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6664</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>群翊</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>229</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>77</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6291</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>沛亨半導</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>228.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>78</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5864</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>致和證</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>226.6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>79</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>8096</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>80</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7805</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>威聯通</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>224.6</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>81</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>閎康科技</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>82</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5009</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>榮剛材料</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>216.9</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>83</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>廣明光電</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>216.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>84</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4971</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IET-KY</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>215.9</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>85</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>營邦</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>213.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>86</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>崇友實業</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>87</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>崑鼎</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>88</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4728</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>雙美</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>89</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>6643</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>M31</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>205</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>90</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>凡甲科技</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>加入 PICKS 抓體檢</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3747,6 +4376,2481 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>收盤</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>市值億</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>18505</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6995.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6680</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6545.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2430</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5372.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1735</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5055.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4828.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>世界先進</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3482.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>力旺電子</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3185</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2378.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8069</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>元太</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>196</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2262.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>522</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>鈊象電子</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>760</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2141.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2285</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>頎邦科技</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>258</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1816.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>657</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1659.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>聖暉*</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1563.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>威剛科技</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>412</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1357.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3665</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1205.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1170</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1148.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>欣銓科技</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1144.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5483</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中美晶</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1112.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3495</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1037.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>雙鴻科技</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E23" t="n">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7734</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>印能科技</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3390</v>
+      </c>
+      <c r="E24" t="n">
+        <v>949.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1355</v>
+      </c>
+      <c r="E25" t="n">
+        <v>932.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7828</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>創新服務</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2240</v>
+      </c>
+      <c r="E26" t="n">
+        <v>907.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>光洋科技</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6548</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>長科*</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>881.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4749</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>新應材</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>917</v>
+      </c>
+      <c r="E29" t="n">
+        <v>868.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>303.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>823.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3363</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>上詮</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>685</v>
+      </c>
+      <c r="E31" t="n">
+        <v>778.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>新普科技</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>417</v>
+      </c>
+      <c r="E32" t="n">
+        <v>771.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>525</v>
+      </c>
+      <c r="E33" t="n">
+        <v>747.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>寶雅國際</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>666</v>
+      </c>
+      <c r="E34" t="n">
+        <v>708.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>波若威</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>868</v>
+      </c>
+      <c r="E35" t="n">
+        <v>699.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>合晶科技</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>679.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>順達科技</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>660.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>環宇-KY</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>536</v>
+      </c>
+      <c r="E38" t="n">
+        <v>648.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>富喬</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>588.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>661</v>
+      </c>
+      <c r="E40" t="n">
+        <v>521.9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>6290</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>良維科技</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>306</v>
+      </c>
+      <c r="E41" t="n">
+        <v>518.7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>家登</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>537</v>
+      </c>
+      <c r="E42" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>信昌電陶</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>285</v>
+      </c>
+      <c r="E43" t="n">
+        <v>490.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>6683</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>雍智科技</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E44" t="n">
+        <v>486.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>649</v>
+      </c>
+      <c r="E45" t="n">
+        <v>460.3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5903</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>420.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4772</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>台特化</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>275</v>
+      </c>
+      <c r="E47" t="n">
+        <v>406.1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>漢磊</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>398.6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7751</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>竑騰</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1475</v>
+      </c>
+      <c r="E49" t="n">
+        <v>396.6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>8415</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>大國鋼</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="E50" t="n">
+        <v>363.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3357</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>臺慶科</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>315</v>
+      </c>
+      <c r="E51" t="n">
+        <v>362.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>8932</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>智通*</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>359.8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>德宏工業</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>279</v>
+      </c>
+      <c r="E53" t="n">
+        <v>354.7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>134</v>
+      </c>
+      <c r="E54" t="n">
+        <v>353.1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>原相科技</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>228</v>
+      </c>
+      <c r="E55" t="n">
+        <v>343.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>中國探針</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>273</v>
+      </c>
+      <c r="E56" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>元大期</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>100</v>
+      </c>
+      <c r="E57" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>8086</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>宏捷科技</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>159.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>313.4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E59" t="n">
+        <v>303.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5371</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>中強光電</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>299.1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>高技企業</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>321.5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>298.9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>鈺創科技</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>91</v>
+      </c>
+      <c r="E62" t="n">
+        <v>298.9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>8064</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>東捷科技</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>156</v>
+      </c>
+      <c r="E63" t="n">
+        <v>288.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>晟德</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>286.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>朋億*</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>368</v>
+      </c>
+      <c r="E65" t="n">
+        <v>286.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>先進光</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>186</v>
+      </c>
+      <c r="E66" t="n">
+        <v>274.2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>6138</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>茂達電子</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>361</v>
+      </c>
+      <c r="E67" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>是方</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>340</v>
+      </c>
+      <c r="E68" t="n">
+        <v>265.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E69" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>8027</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>鈦昇</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>237</v>
+      </c>
+      <c r="E70" t="n">
+        <v>260.7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>6903</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>巨漢</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>381</v>
+      </c>
+      <c r="E71" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>台星科</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>247.3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>8155</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>博智</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>239.3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>3675</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>德微</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>236.4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4743</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>合一</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>233.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>8042</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>金山電子</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="E76" t="n">
+        <v>230.6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>6664</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>群翊</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>6291</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>沛亨半導</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>543</v>
+      </c>
+      <c r="E78" t="n">
+        <v>228.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5864</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>致和證</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="E79" t="n">
+        <v>226.6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>8096</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>224.8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7805</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>威聯通</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>678</v>
+      </c>
+      <c r="E81" t="n">
+        <v>224.6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>閎康科技</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="E82" t="n">
+        <v>217.4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5009</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>榮剛材料</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>36</v>
+      </c>
+      <c r="E83" t="n">
+        <v>216.9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>廣明光電</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="E84" t="n">
+        <v>216.3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>4971</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>IET-KY</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>540</v>
+      </c>
+      <c r="E85" t="n">
+        <v>215.9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>營邦</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>496</v>
+      </c>
+      <c r="E86" t="n">
+        <v>213.2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>崇友實業</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>119</v>
+      </c>
+      <c r="E87" t="n">
+        <v>210.6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>崑鼎</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="E88" t="n">
+        <v>208.6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>4728</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>雙美</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="E89" t="n">
+        <v>205.1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>6643</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>M31</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>490.5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>凡甲科技</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>309</v>
+      </c>
+      <c r="E91" t="n">
+        <v>203.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5530</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>龍巖</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="E92" t="n">
+        <v>203.1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>8255</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>朋程</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="E93" t="n">
+        <v>203.1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>6016</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>康和證券</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="E94" t="n">
+        <v>200.1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>6146</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>耕興</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="E95" t="n">
+        <v>195.1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>建榮工業</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>96</v>
+      </c>
+      <c r="E96" t="n">
+        <v>187.1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3624</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>光頡科技</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>159</v>
+      </c>
+      <c r="E97" t="n">
+        <v>186.6</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>東洋藥品</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="E98" t="n">
+        <v>183.8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5386</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>青雲國際</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>502</v>
+      </c>
+      <c r="E99" t="n">
+        <v>181.1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>4768</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>晶呈科技</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>374</v>
+      </c>
+      <c r="E100" t="n">
+        <v>177.6</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5314</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>世紀*</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="E101" t="n">
+        <v>176.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>OTC排名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>市值億</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>轉上市定位</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>在我們PICKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6995.4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6545.1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5372.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5055.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4828.9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>🔥轉上市即進0050(前50)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>世界先進</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3482.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>力旺電子</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2378.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8069</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>元太</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2262.5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2213</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>鈊象電子</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2141.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2114</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>頎邦科技</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1921</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>⭐轉上市即進51-90</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,23 +778,23 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2147</v>
+        <v>0.127</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -810,55 +810,51 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.63</v>
+        <v>1.56</v>
       </c>
       <c r="L6" t="n">
-        <v>3409.2</v>
+        <v>1863.4</v>
       </c>
       <c r="M6" t="n">
-        <v>192.04</v>
+        <v>21.89</v>
       </c>
       <c r="N6" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="O6" t="n">
-        <v>52.47</v>
+        <v>8.51</v>
       </c>
       <c r="P6" t="n">
-        <v>0.53</v>
+        <v>2.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>103.3</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2285</v>
+        <v>0.1925</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -866,67 +862,67 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>2.4</v>
+        <v>0.98</v>
       </c>
       <c r="L7" t="n">
-        <v>3895.6</v>
+        <v>2750</v>
       </c>
       <c r="M7" t="n">
-        <v>27.34</v>
+        <v>30.1</v>
       </c>
       <c r="N7" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="O7" t="n">
-        <v>4.06</v>
+        <v>5.41</v>
       </c>
       <c r="P7" t="n">
-        <v>3.53</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.7</v>
+        <v>40.4</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.251</v>
+        <v>0.2147</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -934,29 +930,29 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>-0.2</v>
+        <v>0.63</v>
       </c>
       <c r="L8" t="n">
-        <v>2855.6</v>
+        <v>3409.2</v>
       </c>
       <c r="M8" t="n">
-        <v>15.52</v>
+        <v>192.04</v>
       </c>
       <c r="N8" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="O8" t="n">
-        <v>2.53</v>
+        <v>52.47</v>
       </c>
       <c r="P8" t="n">
-        <v>3.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>152.7</v>
+        <v>119.8</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -966,31 +962,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1898</v>
+        <v>0.2285</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -998,59 +994,59 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>1.12</v>
+        <v>2.4</v>
       </c>
       <c r="L9" t="n">
-        <v>2625</v>
+        <v>3895.6</v>
       </c>
       <c r="M9" t="n">
-        <v>57.11</v>
+        <v>27.34</v>
       </c>
       <c r="N9" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="O9" t="n">
-        <v>31.86</v>
+        <v>4.06</v>
       </c>
       <c r="P9" t="n">
-        <v>1.44</v>
+        <v>3.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.300000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1978</v>
+        <v>0.1732</v>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1058,63 +1054,63 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>2.01</v>
+        <v>1.09</v>
       </c>
       <c r="L10" t="n">
-        <v>2778.5</v>
+        <v>2371.3</v>
       </c>
       <c r="M10" t="n">
-        <v>43.57</v>
+        <v>25.23</v>
       </c>
       <c r="N10" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="O10" t="n">
-        <v>4.63</v>
+        <v>3.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.23</v>
+        <v>3.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.2</v>
+        <v>35.3</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1704</v>
+        <v>0.251</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1122,25 +1118,25 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>-1.14</v>
+        <v>-0.2</v>
       </c>
       <c r="L11" t="n">
-        <v>2304.4</v>
+        <v>2855.6</v>
       </c>
       <c r="M11" t="n">
-        <v>16.07</v>
+        <v>15.52</v>
       </c>
       <c r="N11" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>2.53</v>
       </c>
       <c r="P11" t="n">
-        <v>4.99</v>
+        <v>3.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>152.7</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1150,31 +1146,31 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1438</v>
+        <v>0.1898</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1186,51 +1182,47 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>9.07</v>
+        <v>1.12</v>
       </c>
       <c r="L12" t="n">
-        <v>2227.6</v>
+        <v>2625</v>
       </c>
       <c r="M12" t="n">
-        <v>589.23</v>
+        <v>57.11</v>
       </c>
       <c r="N12" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="O12" t="n">
-        <v>4.48</v>
+        <v>31.86</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.2211</v>
+        <v>0.1978</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1238,7 +1230,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1250,115 +1242,107 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>-11.39</v>
+        <v>2.01</v>
       </c>
       <c r="L13" t="n">
-        <v>546.8</v>
+        <v>2778.5</v>
       </c>
       <c r="M13" t="n">
-        <v>18.01</v>
+        <v>43.57</v>
       </c>
       <c r="N13" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>7.25</v>
+        <v>4.63</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>175.8</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>30.2</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1357</v>
+        <v>0.2051</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>-0.89</v>
+        <v>0.89</v>
       </c>
       <c r="L14" t="n">
-        <v>1889</v>
+        <v>2515.2</v>
       </c>
       <c r="M14" t="n">
-        <v>14.17</v>
+        <v>31.35</v>
       </c>
       <c r="N14" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1</v>
+        <v>5.98</v>
       </c>
       <c r="P14" t="n">
-        <v>3.38</v>
+        <v>1.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1226</v>
+        <v>0.1704</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1366,39 +1350,547 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2304.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>52</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>54</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2408</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>64</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3567.1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="N16" t="n">
+        <v>82</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>78</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="E17" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>51</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2227.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>589.23</v>
+      </c>
+      <c r="N17" t="n">
+        <v>96</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>57</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="E18" t="n">
+        <v>43</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>26</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>-11.39</v>
+      </c>
+      <c r="L18" t="n">
+        <v>546.8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>91</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>64</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>聯詠</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="E19" t="n">
+        <v>41</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3310.3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="N19" t="n">
+        <v>97</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>79</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="E20" t="n">
+        <v>38</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>49</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1889</v>
+      </c>
+      <c r="M20" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="N20" t="n">
+        <v>62</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>74</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="E21" t="n">
+        <v>35</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>27</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L21" t="n">
+        <v>626.7</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="N21" t="n">
+        <v>66</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>90</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="E22" t="n">
+        <v>26</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1675</v>
+      </c>
+      <c r="M22" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="N22" t="n">
+        <v>61</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>88</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>36</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
         <v>0.7</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L23" t="n">
         <v>1715.8</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M23" t="n">
         <v>30.21</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N23" t="n">
         <v>90</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O23" t="n">
         <v>1.95</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P23" t="n">
         <v>2.86</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q23" t="n">
         <v>10.6</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1415,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1447,20 +1939,20 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2408</v>
+        <v>0.2011</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1470,20 +1962,20 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2051</v>
+        <v>0.1632</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1493,20 +1985,20 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2011</v>
+        <v>0.1582</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1516,20 +2008,20 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1996</v>
+        <v>0.1339</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1539,20 +2031,20 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1925</v>
+        <v>0.1331</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1562,20 +2054,20 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1732</v>
+        <v>0.1329</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1585,20 +2077,20 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1632</v>
+        <v>0.1316</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1608,20 +2100,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1605</v>
+        <v>0.1265</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1631,20 +2123,20 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1582</v>
+        <v>0.1262</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1654,206 +2146,22 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1339</v>
+        <v>0.1194</v>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>81</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6531</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>愛普*</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.1331</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>82</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.1329</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>83</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>華新科</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.1316</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>84</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>亞翔</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>86</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.1265</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>87</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1262</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>89</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.1194</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>90</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1181</v>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>加入 PICKS 抓體檢</t>
         </is>
@@ -1870,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3131,54 +3439,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2331</v>
+        <v>0.2408</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.2285</v>
+        <v>0.2331</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3189,25 +3497,25 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.2211</v>
+        <v>0.2285</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3218,25 +3526,25 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2147</v>
+        <v>0.2211</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3247,29 +3555,25 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2056</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2147</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3280,25 +3584,29 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.1978</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>0.2056</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3309,20 +3617,20 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.1898</v>
+        <v>0.2051</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
@@ -3338,49 +3646,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.1883</v>
+        <v>0.1996</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.1704</v>
+        <v>0.1978</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
@@ -3390,32 +3698,28 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.1925</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>B</t>
@@ -3423,26 +3727,26 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.1514</v>
+        <v>0.1898</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
@@ -3458,25 +3762,25 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.1438</v>
+        <v>0.1883</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3487,54 +3791,58 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.1357</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
+        <v>0.185</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.1226</v>
+        <v>0.1732</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3545,112 +3853,116 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.1176</v>
+        <v>0.1704</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.1001</v>
+        <v>0.1605</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+        <v>0.153</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.0946</v>
+        <v>0.1514</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3661,25 +3973,25 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.0784</v>
+        <v>0.1438</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3690,25 +4002,25 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0764</v>
+        <v>0.1357</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3719,25 +4031,25 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0757</v>
+        <v>0.127</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3748,49 +4060,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1226</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0738</v>
+        <v>0.1181</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
@@ -3806,25 +4118,25 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0731</v>
+        <v>0.1176</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3835,49 +4147,49 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.0727</v>
+        <v>0.1001</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.0693</v>
+        <v>0.099</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -3893,25 +4205,25 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.0667</v>
+        <v>0.0946</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3922,20 +4234,20 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.0658</v>
+        <v>0.0784</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
@@ -3951,107 +4263,107 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0599</v>
+        <v>0.0764</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0576</v>
+        <v>0.0757</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>群益證</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0575</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0547</v>
+        <v>0.0738</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
@@ -4061,26 +4373,26 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.0537</v>
+        <v>0.0731</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
@@ -4096,25 +4408,25 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.0523</v>
+        <v>0.0727</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4125,54 +4437,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0521</v>
+        <v>0.0693</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0491</v>
+        <v>0.0667</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4183,54 +4495,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0479</v>
+        <v>0.0658</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0467</v>
+        <v>0.0599</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4241,20 +4553,20 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.0445</v>
+        <v>0.0576</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
@@ -4264,60 +4576,60 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>大同</t>
+          <t>群益證</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.0441</v>
+        <v>0.0575</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0429</v>
+        <v>0.0547</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4328,20 +4640,20 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0426</v>
+        <v>0.0537</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
@@ -4357,136 +4669,136 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>台灣精銳</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.0396</v>
+        <v>0.0523</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0385</v>
+        <v>0.0521</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.038</v>
+        <v>0.0491</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0367</v>
+        <v>0.0479</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.0354</v>
+        <v>0.0467</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
@@ -4496,55 +4808,55 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>定穎投控</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.0338</v>
+        <v>0.0445</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>潤泰全</t>
+          <t>大同</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.0334</v>
+        <v>0.0441</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
@@ -4554,31 +4866,31 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>531</v>
+        <v>161</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>晶彩科</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.0067</v>
+        <v>0.0429</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4589,49 +4901,49 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>532</v>
+        <v>164</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.0067</v>
+        <v>0.0426</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>560</v>
+        <v>172</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>台灣精銳</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.0061</v>
+        <v>0.0396</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
@@ -4647,54 +4959,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>584</v>
+        <v>177</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.0056</v>
+        <v>0.0385</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>587</v>
+        <v>178</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>豐達科</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.0055</v>
+        <v>0.038</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4705,194 +5017,194 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>589</v>
+        <v>180</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>國票金</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0054</v>
+        <v>0.0367</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>590</v>
+        <v>189</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.0054</v>
+        <v>0.0354</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>613</v>
+        <v>196</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>一零四</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.005</v>
+        <v>0.0338</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>655</v>
+        <v>200</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>潤泰全</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.0043</v>
+        <v>0.0334</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>661</v>
+        <v>531</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>凌群</t>
+          <t>晶彩科</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0042</v>
+        <v>0.0067</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>695</v>
+        <v>532</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.0037</v>
+        <v>0.0067</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>701</v>
+        <v>560</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.0036</v>
+        <v>0.0061</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
@@ -4908,20 +5220,20 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>710</v>
+        <v>584</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0035</v>
+        <v>0.0056</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
@@ -4930,6 +5242,267 @@
         </is>
       </c>
       <c r="G102" t="inlineStr">
+        <is>
+          <t>🟡合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>587</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>589</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>7730</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>暉盛-創</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>590</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>9918</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>欣天然</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>613</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>一零四</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>655</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>台耀</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>661</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>695</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6776</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>展碁國際</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>701</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>邁達特</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>710</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>訊連</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
         <is>
           <t>🟢便宜</t>
         </is>
@@ -7087,7 +7660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7179,23 +7752,23 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>273</v>
+        <v>298.9</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7203,11 +7776,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -7215,22 +7788,22 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>1.21</v>
+        <v>0.92</v>
       </c>
       <c r="L2" t="n">
-        <v>27.9</v>
+        <v>21</v>
       </c>
       <c r="M2" t="n">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>8.57</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.79</v>
+        <v>2.24</v>
       </c>
       <c r="P2" t="n">
-        <v>15.4</v>
+        <v>58.3</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -7240,31 +7813,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>210.6</v>
+        <v>343.1</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -7276,109 +7849,117 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="L3" t="n">
-        <v>17.12</v>
+        <v>20.19</v>
       </c>
       <c r="M3" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="N3" t="n">
-        <v>3.39</v>
+        <v>3.02</v>
       </c>
       <c r="O3" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>10.3</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>262</v>
+        <v>313.4</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="L4" t="n">
-        <v>62.01</v>
+        <v>35.84</v>
       </c>
       <c r="M4" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="N4" t="n">
-        <v>32.45</v>
+        <v>3.82</v>
       </c>
       <c r="O4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>雙美</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>205.1</v>
+        <v>273</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -7390,44 +7971,48 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="L5" t="n">
-        <v>28.33</v>
+        <v>27.9</v>
       </c>
       <c r="M5" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N5" t="n">
-        <v>17.29</v>
+        <v>8.57</v>
       </c>
       <c r="O5" t="n">
-        <v>3.21</v>
+        <v>2.79</v>
       </c>
       <c r="P5" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>247.3</v>
+        <v>298.9</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -7435,7 +8020,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -7443,117 +8028,117 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="L6" t="n">
-        <v>33.95</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="N6" t="n">
-        <v>4.37</v>
+        <v>6.29</v>
       </c>
       <c r="O6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>605.5</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>288.3</v>
+        <v>210.6</v>
       </c>
       <c r="E7" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
-        <v>70.13</v>
+        <v>17.12</v>
       </c>
       <c r="M7" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="N7" t="n">
-        <v>7.07</v>
+        <v>3.39</v>
       </c>
       <c r="O7" t="n">
-        <v>0.59</v>
+        <v>4.45</v>
       </c>
       <c r="P7" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>217.4</v>
+        <v>262</v>
       </c>
       <c r="E8" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -7561,52 +8146,48 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>1.15</v>
       </c>
       <c r="L8" t="n">
-        <v>40.16</v>
+        <v>62.01</v>
       </c>
       <c r="M8" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="N8" t="n">
-        <v>4.01</v>
+        <v>32.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>99.3</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>208.6</v>
+        <v>286.8</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7614,64 +8195,68 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>-0.87</v>
+        <v>0.01</v>
       </c>
       <c r="L9" t="n">
-        <v>15.6</v>
+        <v>2.62</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.33</v>
+        <v>0.98</v>
       </c>
       <c r="O9" t="n">
-        <v>5.48</v>
+        <v>6.03</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>8.1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>雙美</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>260.7</v>
+        <v>205.1</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -7679,89 +8264,626 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>-3.66</v>
+        <v>1.13</v>
       </c>
       <c r="L10" t="n">
-        <v>251.19</v>
+        <v>28.33</v>
       </c>
       <c r="M10" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="N10" t="n">
-        <v>9.4</v>
+        <v>17.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="P10" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>23.8</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>274.2</v>
+        <v>247.3</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L11" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="M11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P11" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>53</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>朋億*</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>286.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L13" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="M13" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P13" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>58</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>303.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>69</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L14" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="M14" t="n">
+        <v>71</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>59</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5371</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>62</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8064</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>東捷</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>288.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>38</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>49</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L16" t="n">
+        <v>70.13</v>
+      </c>
+      <c r="M16" t="n">
+        <v>79</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>81</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>閎康</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>38</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>38</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="M17" t="n">
+        <v>97</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P17" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>87</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>崑鼎</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>31</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>36</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="L18" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>69</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>8027</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>鈦昇</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>260.7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="L19" t="n">
+        <v>251.19</v>
+      </c>
+      <c r="M19" t="n">
+        <v>93</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>65</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>先進光</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>23</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
         <v>-0.67</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L20" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M20" t="n">
         <v>52</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N20" t="n">
         <v>8.01</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P20" t="n">
         <v>-13.9</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7778,7 +8900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7856,20 +8978,20 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>中國探針</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>353.1</v>
+        <v>320</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -7879,20 +9001,20 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>元大期</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>343.1</v>
+        <v>320</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -7902,20 +9024,20 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>中國探針</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>320</v>
+        <v>265.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -7925,20 +9047,20 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>元大期</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>320</v>
+        <v>254</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7948,20 +9070,20 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宏捷科技</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>313.4</v>
+        <v>239.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -7971,20 +9093,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>德微</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>303.3</v>
+        <v>236.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -7994,20 +9116,20 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中強光電</t>
+          <t>合一</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>299.1</v>
+        <v>233.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -8017,20 +9139,20 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>高技企業</t>
+          <t>金山電子</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>298.9</v>
+        <v>230.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -8040,20 +9162,20 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>鈺創科技</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>298.9</v>
+        <v>229</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -8063,20 +9185,20 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>沛亨半導</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>286.8</v>
+        <v>228.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -8086,20 +9208,20 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>致和證</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>286.3</v>
+        <v>226.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -8109,20 +9231,20 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>265.1</v>
+        <v>224.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -8132,20 +9254,20 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>254</v>
+        <v>224.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -8155,20 +9277,20 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>榮剛材料</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>239.3</v>
+        <v>216.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -8178,20 +9300,20 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>德微</t>
+          <t>廣明光電</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>236.4</v>
+        <v>216.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -8201,20 +9323,20 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>合一</t>
+          <t>IET-KY</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>233.5</v>
+        <v>215.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -8224,20 +9346,20 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>金山電子</t>
+          <t>營邦</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>230.6</v>
+        <v>213.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -8247,20 +9369,20 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -8270,229 +9392,22 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>沛亨半導</t>
+          <t>凡甲科技</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>228.1</v>
+        <v>203.5</v>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>78</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>5864</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>致和證</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>226.6</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>79</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>8096</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>224.8</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>80</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>7805</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>威聯通</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>224.6</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>82</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>5009</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>榮剛材料</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>216.9</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>83</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>6188</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>廣明光電</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>216.3</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>84</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>4971</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>IET-KY</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>215.9</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>85</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3693</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>營邦</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>213.2</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>89</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>6643</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>M31</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>205</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>90</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3526</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>凡甲科技</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="E31" t="inlineStr">
         <is>
           <t>加入 PICKS 抓體檢</t>
         </is>
@@ -10847,7 +11762,11 @@
           <t>⭐轉上市即進51-90</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10871,7 +11790,11 @@
           <t>⭐轉上市即進51-90</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10895,7 +11818,11 @@
           <t>⭐轉上市即進51-90</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -11003,7 +11930,11 @@
           <t>⭐轉上市即進51-90</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11068,7 +11999,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -11078,7 +12009,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -11088,7 +12019,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -11098,7 +12029,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候選A_已體檢" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候選B_blind_spot" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="universe在TWSE排名" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TWSE前100" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富櫃50候選A_已體檢" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富櫃50候選B_blind" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OTC前100" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OTC轉上市觀察" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="門檻說明" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="候選A_已體檢" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="候選B_blind_spot" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="universe在TWSE排名" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TWSE前100" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="富櫃50候選A_已體檢" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="富櫃50候選B_blind" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="OTC前100" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="OTC轉上市觀察" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="門檻說明" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,96 +421,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>未來估值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ForwardPE</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>成長率g%</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>市值(億)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -530,147 +538,167 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2429</v>
+        <v>0.1883</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.92</v>
+      </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>21.2</v>
       </c>
       <c r="L2" t="n">
-        <v>4027</v>
+        <v>29.8</v>
       </c>
       <c r="M2" t="n">
-        <v>65.19</v>
-      </c>
-      <c r="N2" t="n">
-        <v>59</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.25</v>
-      </c>
+        <v>1.13</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>27.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U2" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1883</v>
+        <v>0.1514</v>
       </c>
       <c r="E3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="R3" t="n">
+        <v>96</v>
+      </c>
+      <c r="S3" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="U3" t="n">
         <v>85</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2974.9</v>
-      </c>
-      <c r="M3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2331</v>
+        <v>0.127</v>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -678,120 +706,136 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4</v>
+      </c>
       <c r="K4" t="n">
-        <v>1.62</v>
+        <v>14.2</v>
       </c>
       <c r="L4" t="n">
-        <v>3092.8</v>
+        <v>54.3</v>
       </c>
       <c r="M4" t="n">
-        <v>45.77</v>
-      </c>
-      <c r="N4" t="n">
-        <v>97</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>6.6</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>1.08</v>
+        <v>1863.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>21.89</v>
+      </c>
+      <c r="R4" t="n">
+        <v>74</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U4" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1514</v>
+        <v>0.2429</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2439.5</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>23.77</v>
-      </c>
-      <c r="N5" t="n">
-        <v>96</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.13</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>85</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>65.19</v>
+      </c>
+      <c r="R5" t="n">
+        <v>59</v>
+      </c>
+      <c r="S5" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.127</v>
+        <v>0.2331</v>
       </c>
       <c r="E6" t="n">
         <v>78</v>
@@ -802,59 +846,65 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1863.4</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="N6" t="n">
-        <v>74</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.91</v>
-      </c>
+        <v>1.62</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>45.77</v>
+      </c>
+      <c r="R6" t="n">
+        <v>97</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="U6" t="n">
+        <v>13</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1925</v>
+        <v>0.1732</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -866,179 +916,209 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1.35</v>
+      </c>
       <c r="K7" t="n">
-        <v>0.98</v>
+        <v>21.3</v>
       </c>
       <c r="L7" t="n">
-        <v>2750</v>
+        <v>18.7</v>
       </c>
       <c r="M7" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>66</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.41</v>
+        <v>1.09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2371.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>25.23</v>
+      </c>
+      <c r="R7" t="n">
+        <v>72</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="U7" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2147</v>
+        <v>0.1925</v>
       </c>
       <c r="E8" t="n">
+        <v>75</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>73</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>84</v>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3.06</v>
+      </c>
       <c r="K8" t="n">
-        <v>0.63</v>
+        <v>27.4</v>
       </c>
       <c r="L8" t="n">
-        <v>3409.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>192.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>98</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>52.47</v>
+        <v>0.98</v>
       </c>
       <c r="P8" t="n">
-        <v>0.53</v>
+        <v>2750</v>
       </c>
       <c r="Q8" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>30.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>66</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2285</v>
+        <v>0.2147</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3895.6</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>27.34</v>
-      </c>
-      <c r="N9" t="n">
-        <v>95</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.53</v>
-      </c>
+        <v>0.63</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
+        <v>192.04</v>
+      </c>
+      <c r="R9" t="n">
+        <v>98</v>
+      </c>
+      <c r="S9" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="U9" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1732</v>
+        <v>0.2285</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1046,39 +1126,51 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M10" t="n">
         <v>3</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2371.3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="N10" t="n">
-        <v>72</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.03</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>27.34</v>
+      </c>
+      <c r="R10" t="n">
+        <v>95</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="U10" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1113,32 +1205,34 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L11" t="n">
-        <v>2855.6</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
         <v>15.52</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>68</v>
       </c>
-      <c r="O11" t="n">
+      <c r="S11" t="n">
         <v>2.53</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
         <v>3.47</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="U11" t="n">
         <v>152.7</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1177,32 +1271,44 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K12" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>1.12</v>
       </c>
-      <c r="L12" t="n">
-        <v>2625</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
         <v>57.11</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
         <v>84</v>
       </c>
-      <c r="O12" t="n">
+      <c r="S12" t="n">
         <v>31.86</v>
       </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="U12" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1237,32 +1343,42 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>2</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
         <v>2.01</v>
       </c>
-      <c r="L13" t="n">
-        <v>2778.5</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
         <v>43.57</v>
       </c>
-      <c r="N13" t="n">
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="O13" t="n">
+      <c r="S13" t="n">
         <v>4.63</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
         <v>1.23</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="U13" t="n">
         <v>30.2</v>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1297,32 +1413,46 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K14" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>0.89</v>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>2515.2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>31.35</v>
       </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>96</v>
       </c>
-      <c r="O14" t="n">
+      <c r="S14" t="n">
         <v>5.98</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="U14" t="n">
         <v>9</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1357,32 +1487,34 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
         <v>-1.14</v>
       </c>
-      <c r="L15" t="n">
-        <v>2304.4</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="n">
         <v>16.07</v>
       </c>
-      <c r="N15" t="n">
+      <c r="R15" t="n">
         <v>52</v>
       </c>
-      <c r="O15" t="n">
+      <c r="S15" t="n">
         <v>1.43</v>
       </c>
-      <c r="P15" t="n">
+      <c r="T15" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="U15" t="n">
         <v>5</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1421,32 +1553,46 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K16" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
         <v>0.26</v>
       </c>
-      <c r="L16" t="n">
+      <c r="P16" t="n">
         <v>3567.1</v>
       </c>
-      <c r="M16" t="n">
+      <c r="Q16" t="n">
         <v>63.77</v>
       </c>
-      <c r="N16" t="n">
+      <c r="R16" t="n">
         <v>82</v>
       </c>
-      <c r="O16" t="n">
+      <c r="S16" t="n">
         <v>8.27</v>
       </c>
-      <c r="P16" t="n">
+      <c r="T16" t="n">
         <v>0.78</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="U16" t="n">
         <v>-33.5</v>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1481,32 +1627,34 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
         <v>9.07</v>
       </c>
-      <c r="L17" t="n">
-        <v>2227.6</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
         <v>589.23</v>
       </c>
-      <c r="N17" t="n">
+      <c r="R17" t="n">
         <v>96</v>
       </c>
-      <c r="O17" t="n">
+      <c r="S17" t="n">
         <v>4.48</v>
       </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="U17" t="n">
         <v>17.7</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1545,32 +1693,34 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
         <v>-11.39</v>
       </c>
-      <c r="L18" t="n">
-        <v>546.8</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
         <v>18.01</v>
       </c>
-      <c r="N18" t="n">
+      <c r="R18" t="n">
         <v>91</v>
       </c>
-      <c r="O18" t="n">
+      <c r="S18" t="n">
         <v>7.25</v>
       </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="U18" t="n">
         <v>175.8</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1609,32 +1759,36 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
         <v>1.01</v>
       </c>
-      <c r="L19" t="n">
+      <c r="P19" t="n">
         <v>3310.3</v>
       </c>
-      <c r="M19" t="n">
+      <c r="Q19" t="n">
         <v>22.29</v>
       </c>
-      <c r="N19" t="n">
+      <c r="R19" t="n">
         <v>97</v>
       </c>
-      <c r="O19" t="n">
+      <c r="S19" t="n">
         <v>4.6</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
         <v>4.23</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="U19" t="n">
         <v>9.4</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1673,32 +1827,34 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>3</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
         <v>-0.89</v>
       </c>
-      <c r="L20" t="n">
-        <v>1889</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
         <v>14.17</v>
       </c>
-      <c r="N20" t="n">
+      <c r="R20" t="n">
         <v>62</v>
       </c>
-      <c r="O20" t="n">
+      <c r="S20" t="n">
         <v>2.1</v>
       </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="U20" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1737,32 +1893,36 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
         <v>0.36</v>
       </c>
-      <c r="L21" t="n">
+      <c r="P21" t="n">
         <v>626.7</v>
       </c>
-      <c r="M21" t="n">
+      <c r="Q21" t="n">
         <v>86.45999999999999</v>
       </c>
-      <c r="N21" t="n">
+      <c r="R21" t="n">
         <v>66</v>
       </c>
-      <c r="O21" t="n">
+      <c r="S21" t="n">
         <v>6.57</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="U21" t="n">
         <v>31.6</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1801,32 +1961,36 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>2</v>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
         <v>0.93</v>
       </c>
-      <c r="L22" t="n">
+      <c r="P22" t="n">
         <v>1675</v>
       </c>
-      <c r="M22" t="n">
+      <c r="Q22" t="n">
         <v>27.19</v>
       </c>
-      <c r="N22" t="n">
+      <c r="R22" t="n">
         <v>61</v>
       </c>
-      <c r="O22" t="n">
+      <c r="S22" t="n">
         <v>1.02</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>1.32</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="U22" t="n">
         <v>11.1</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1865,32 +2029,34 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
         <v>0.7</v>
       </c>
-      <c r="L23" t="n">
-        <v>1715.8</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="n">
         <v>30.21</v>
       </c>
-      <c r="N23" t="n">
+      <c r="R23" t="n">
         <v>90</v>
       </c>
-      <c r="O23" t="n">
+      <c r="S23" t="n">
         <v>1.95</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
         <v>2.86</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="U23" t="n">
         <v>10.6</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1911,27 +2077,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -2182,37 +2348,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>是否0050</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -5523,27 +5689,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -7660,91 +7826,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OTC市值億</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>未來估值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ForwardPE</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>成長率g%</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -7783,29 +7969,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>0.92</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>21</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>56</v>
       </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
         <v>7</v>
       </c>
-      <c r="O2" t="n">
+      <c r="S2" t="n">
         <v>2.24</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
         <v>58.3</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7844,29 +8034,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>1.53</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>20.19</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>72</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>3.02</v>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
         <v>4.43</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7905,29 +8099,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>1.85</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>35.84</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>40</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>3.82</v>
       </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
         <v>1.05</v>
       </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
         <v>37</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7966,29 +8164,33 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>1.21</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>27.9</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>91</v>
       </c>
-      <c r="N5" t="n">
+      <c r="R5" t="n">
         <v>8.57</v>
       </c>
-      <c r="O5" t="n">
+      <c r="S5" t="n">
         <v>2.79</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
         <v>15.4</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7996,121 +8198,139 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>298.9</v>
+        <v>210.6</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M6" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="L6" t="n">
-        <v>94.79000000000001</v>
-      </c>
-      <c r="M6" t="n">
-        <v>85</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6.29</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>605.5</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>17.12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>55</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>210.6</v>
+        <v>298.9</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="L7" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="M7" t="n">
-        <v>55</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.39</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>4.45</v>
+        <v>1.85</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>94.79000000000001</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>85</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>605.5</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -8145,29 +8365,43 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K8" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>60</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>1.15</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>62.01</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>83</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>32.45</v>
       </c>
-      <c r="O8" t="n">
+      <c r="S8" t="n">
         <v>1.09</v>
       </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
         <v>99.3</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8202,29 +8436,33 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>0.01</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>2.62</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
         <v>0.98</v>
       </c>
-      <c r="O9" t="n">
+      <c r="S9" t="n">
         <v>6.03</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
         <v>8.1</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8263,29 +8501,43 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M10" t="n">
         <v>3</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>1.13</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>28.33</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>74</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>17.29</v>
       </c>
-      <c r="O10" t="n">
+      <c r="S10" t="n">
         <v>3.21</v>
       </c>
-      <c r="P10" t="n">
+      <c r="T10" t="n">
         <v>23.8</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8320,29 +8572,41 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>2</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
+        <v>36</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>1.67</v>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>33.95</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>100</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>4.37</v>
       </c>
-      <c r="O11" t="n">
+      <c r="S11" t="n">
         <v>2.12</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
         <v>22.1</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8377,29 +8641,33 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>2.14</v>
       </c>
-      <c r="L12" t="n">
+      <c r="P12" t="n">
         <v>58.01</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
         <v>4.14</v>
       </c>
-      <c r="O12" t="n">
+      <c r="S12" t="n">
         <v>1.51</v>
       </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8438,29 +8706,33 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
         <v>0.92</v>
       </c>
-      <c r="L13" t="n">
+      <c r="P13" t="n">
         <v>25.88</v>
       </c>
-      <c r="M13" t="n">
+      <c r="Q13" t="n">
         <v>100</v>
       </c>
-      <c r="N13" t="n">
+      <c r="R13" t="n">
         <v>5.6</v>
       </c>
-      <c r="O13" t="n">
+      <c r="S13" t="n">
         <v>2.72</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
         <v>81.7</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8499,29 +8771,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>0.68</v>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>64.42</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>71</v>
       </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>9.17</v>
       </c>
-      <c r="O14" t="n">
+      <c r="S14" t="n">
         <v>1.43</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
         <v>-43.4</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8529,23 +8805,23 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>299.1</v>
+        <v>208.6</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -8553,60 +8829,70 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2.52</v>
+      </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>14.7</v>
       </c>
       <c r="L15" t="n">
-        <v>127.5</v>
+        <v>6.2</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.13</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>0.65</v>
+        <v>-0.87</v>
       </c>
       <c r="P15" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>288.3</v>
+        <v>299.1</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -8614,36 +8900,40 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="L16" t="n">
-        <v>70.13</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>79</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.07</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>0.59</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+        <v>127.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>100</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8651,20 +8941,20 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>217.4</v>
+        <v>288.3</v>
       </c>
       <c r="E17" t="n">
         <v>38</v>
@@ -8675,36 +8965,40 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="M17" t="n">
-        <v>97</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.01</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+        <v>70.13</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>79</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8712,23 +9006,23 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>208.6</v>
+        <v>217.4</v>
       </c>
       <c r="E18" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -8736,36 +9030,44 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="L18" t="n">
-        <v>15.6</v>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.33</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>5.48</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>40.16</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>97</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T18" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8800,29 +9102,33 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
         <v>-3.66</v>
       </c>
-      <c r="L19" t="n">
+      <c r="P19" t="n">
         <v>251.19</v>
       </c>
-      <c r="M19" t="n">
+      <c r="Q19" t="n">
         <v>93</v>
       </c>
-      <c r="N19" t="n">
+      <c r="R19" t="n">
         <v>9.4</v>
       </c>
-      <c r="O19" t="n">
+      <c r="S19" t="n">
         <v>0</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
         <v>140.2</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8861,29 +9167,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
         <v>-0.67</v>
       </c>
-      <c r="L20" t="n">
+      <c r="P20" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="M20" t="n">
+      <c r="Q20" t="n">
         <v>52</v>
       </c>
-      <c r="N20" t="n">
+      <c r="R20" t="n">
         <v>8.01</v>
       </c>
-      <c r="O20" t="n">
+      <c r="S20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
         <v>-13.9</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8904,27 +9214,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -9428,27 +9738,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>收盤</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -11569,32 +11879,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>轉上市定位</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>在我們PICKS</t>
         </is>
@@ -11951,12 +12261,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>值</t>
         </is>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -590,7 +590,9 @@
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>2974.9</v>
+      </c>
       <c r="Q2" t="n">
         <v>27.5</v>
       </c>
@@ -662,7 +664,9 @@
       <c r="O3" t="n">
         <v>2.64</v>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>2439.5</v>
+      </c>
       <c r="Q3" t="n">
         <v>23.77</v>
       </c>
@@ -798,7 +802,9 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>4027</v>
+      </c>
       <c r="Q5" t="n">
         <v>65.19</v>
       </c>
@@ -864,7 +870,9 @@
       <c r="O6" t="n">
         <v>1.62</v>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>3092.8</v>
+      </c>
       <c r="Q6" t="n">
         <v>45.77</v>
       </c>
@@ -1078,7 +1086,9 @@
       <c r="O9" t="n">
         <v>0.63</v>
       </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>3409.2</v>
+      </c>
       <c r="Q9" t="n">
         <v>192.04</v>
       </c>
@@ -1154,7 +1164,9 @@
       <c r="O10" t="n">
         <v>2.4</v>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>3895.6</v>
+      </c>
       <c r="Q10" t="n">
         <v>27.34</v>
       </c>
@@ -1216,7 +1228,9 @@
       <c r="O11" t="n">
         <v>-0.2</v>
       </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>2855.6</v>
+      </c>
       <c r="Q11" t="n">
         <v>15.52</v>
       </c>
@@ -1292,7 +1306,9 @@
       <c r="O12" t="n">
         <v>1.12</v>
       </c>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>2625</v>
+      </c>
       <c r="Q12" t="n">
         <v>57.11</v>
       </c>
@@ -1362,7 +1378,9 @@
       <c r="O13" t="n">
         <v>2.01</v>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>2778.5</v>
+      </c>
       <c r="Q13" t="n">
         <v>43.57</v>
       </c>
@@ -1498,7 +1516,9 @@
       <c r="O15" t="n">
         <v>-1.14</v>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>2304.4</v>
+      </c>
       <c r="Q15" t="n">
         <v>16.07</v>
       </c>
@@ -1638,7 +1658,9 @@
       <c r="O17" t="n">
         <v>9.07</v>
       </c>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>2227.6</v>
+      </c>
       <c r="Q17" t="n">
         <v>589.23</v>
       </c>
@@ -1704,7 +1726,9 @@
       <c r="O18" t="n">
         <v>-11.39</v>
       </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>546.8</v>
+      </c>
       <c r="Q18" t="n">
         <v>18.01</v>
       </c>
@@ -1838,7 +1862,9 @@
       <c r="O20" t="n">
         <v>-0.89</v>
       </c>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>1889</v>
+      </c>
       <c r="Q20" t="n">
         <v>14.17</v>
       </c>
@@ -2040,7 +2066,9 @@
       <c r="O23" t="n">
         <v>0.7</v>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>1715.8</v>
+      </c>
       <c r="Q23" t="n">
         <v>30.21</v>
       </c>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="候選A_已體檢" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="候選B_blind_spot" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="universe在TWSE排名" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TWSE前100" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="富櫃50候選A_已體檢" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="富櫃50候選B_blind" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="OTC前100" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="OTC轉上市觀察" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="門檻說明" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候選A_已體檢" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候選B_blind_spot" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="universe在TWSE排名" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TWSE前100" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富櫃50候選A_已體檢" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富櫃50候選B_blind" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OTC前100" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OTC轉上市觀察" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="門檻說明" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,13 +25,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,116 +433,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>未來估值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>PEG</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ForwardPE</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>成長率g%</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>市值(億)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -538,97 +530,87 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1883</v>
+        <v>0.2429</v>
       </c>
       <c r="E2" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.92</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>21.2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>29.8</v>
+        <v>4027</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>65.19</v>
+      </c>
+      <c r="N2" t="n">
+        <v>59</v>
+      </c>
       <c r="O2" t="n">
-        <v>1.13</v>
+        <v>11.44</v>
       </c>
       <c r="P2" t="n">
-        <v>2974.9</v>
+        <v>0.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>100</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U2" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>108.5</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1514</v>
+        <v>0.1883</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -636,73 +618,59 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2974.9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="N3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>2.64</v>
+        <v>5.1</v>
       </c>
       <c r="P3" t="n">
-        <v>2439.5</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.77</v>
-      </c>
-      <c r="R3" t="n">
-        <v>96</v>
-      </c>
-      <c r="S3" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="U3" t="n">
-        <v>85</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
+        <v>46.6</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.127</v>
+        <v>0.2331</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -710,138 +678,120 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>14.2</v>
+        <v>1.62</v>
       </c>
       <c r="L4" t="n">
-        <v>54.3</v>
+        <v>3092.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>45.77</v>
+      </c>
+      <c r="N4" t="n">
+        <v>97</v>
+      </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>6.6</v>
       </c>
       <c r="P4" t="n">
-        <v>1863.4</v>
+        <v>1.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="R4" t="n">
-        <v>74</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U4" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2429</v>
+        <v>0.1514</v>
       </c>
       <c r="E5" t="n">
+        <v>78</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2439.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="N5" t="n">
+        <v>96</v>
+      </c>
+      <c r="O5" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="Q5" t="n">
         <v>85</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>66</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4027</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>65.19</v>
-      </c>
-      <c r="R5" t="n">
-        <v>59</v>
-      </c>
-      <c r="S5" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2331</v>
+        <v>0.127</v>
       </c>
       <c r="E6" t="n">
         <v>78</v>
@@ -852,67 +802,59 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1863.4</v>
+      </c>
       <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>21.89</v>
+      </c>
+      <c r="N6" t="n">
+        <v>74</v>
+      </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>8.51</v>
       </c>
       <c r="P6" t="n">
-        <v>3092.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>45.77</v>
-      </c>
-      <c r="R6" t="n">
-        <v>97</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="U6" t="n">
-        <v>13</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>103.3</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1732</v>
+        <v>0.1925</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -924,211 +866,179 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1.35</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>21.3</v>
+        <v>0.98</v>
       </c>
       <c r="L7" t="n">
-        <v>18.7</v>
+        <v>2750</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>30.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>66</v>
+      </c>
       <c r="O7" t="n">
-        <v>1.09</v>
+        <v>5.41</v>
       </c>
       <c r="P7" t="n">
-        <v>2371.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="R7" t="n">
-        <v>72</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="U7" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
+        <v>40.4</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1925</v>
+        <v>0.2147</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>3.06</v>
-      </c>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>27.4</v>
+        <v>0.63</v>
       </c>
       <c r="L8" t="n">
-        <v>9.800000000000001</v>
+        <v>3409.2</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>192.04</v>
+      </c>
+      <c r="N8" t="n">
+        <v>98</v>
+      </c>
       <c r="O8" t="n">
-        <v>0.98</v>
+        <v>52.47</v>
       </c>
       <c r="P8" t="n">
-        <v>2750</v>
+        <v>0.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>66</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
+        <v>119.8</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2147</v>
+        <v>0.2285</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3895.6</v>
+      </c>
       <c r="M9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>27.34</v>
+      </c>
+      <c r="N9" t="n">
+        <v>95</v>
+      </c>
       <c r="O9" t="n">
-        <v>0.63</v>
+        <v>4.06</v>
       </c>
       <c r="P9" t="n">
-        <v>3409.2</v>
+        <v>3.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>192.04</v>
-      </c>
-      <c r="R9" t="n">
-        <v>98</v>
-      </c>
-      <c r="S9" t="n">
-        <v>52.47</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="U9" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2285</v>
+        <v>0.1732</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1136,53 +1046,39 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>4.94</v>
-      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>25.9</v>
+        <v>1.09</v>
       </c>
       <c r="L10" t="n">
-        <v>5.5</v>
+        <v>2371.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>25.23</v>
+      </c>
+      <c r="N10" t="n">
+        <v>72</v>
+      </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>3.23</v>
       </c>
       <c r="P10" t="n">
-        <v>3895.6</v>
+        <v>3.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.34</v>
-      </c>
-      <c r="R10" t="n">
-        <v>95</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="U10" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
+        <v>35.3</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1217,36 +1113,32 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2855.6</v>
+      </c>
       <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>15.52</v>
+      </c>
+      <c r="N11" t="n">
+        <v>68</v>
+      </c>
       <c r="O11" t="n">
-        <v>-0.2</v>
+        <v>2.53</v>
       </c>
       <c r="P11" t="n">
-        <v>2855.6</v>
+        <v>3.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.52</v>
-      </c>
-      <c r="R11" t="n">
-        <v>68</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="U11" t="n">
         <v>152.7</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1285,46 +1177,32 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>2.83</v>
-      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>47.5</v>
+        <v>1.12</v>
       </c>
       <c r="L12" t="n">
-        <v>20.2</v>
+        <v>2625</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>57.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>84</v>
+      </c>
       <c r="O12" t="n">
-        <v>1.12</v>
+        <v>31.86</v>
       </c>
       <c r="P12" t="n">
-        <v>2625</v>
+        <v>1.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>57.11</v>
-      </c>
-      <c r="R12" t="n">
-        <v>84</v>
-      </c>
-      <c r="S12" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U12" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1359,44 +1237,32 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
+      <c r="I13" t="n">
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>52.2</v>
+        <v>2.01</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.5</v>
+        <v>2778.5</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>43.57</v>
+      </c>
+      <c r="N13" t="n">
+        <v>100</v>
+      </c>
       <c r="O13" t="n">
-        <v>2.01</v>
+        <v>4.63</v>
       </c>
       <c r="P13" t="n">
-        <v>2778.5</v>
+        <v>1.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>43.57</v>
-      </c>
-      <c r="R13" t="n">
-        <v>100</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="U13" t="n">
         <v>30.2</v>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1431,46 +1297,32 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1.76</v>
-      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>26.6</v>
+        <v>0.89</v>
       </c>
       <c r="L14" t="n">
-        <v>17.8</v>
+        <v>2515.2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>31.35</v>
+      </c>
+      <c r="N14" t="n">
+        <v>96</v>
+      </c>
       <c r="O14" t="n">
-        <v>0.89</v>
+        <v>5.98</v>
       </c>
       <c r="P14" t="n">
-        <v>2515.2</v>
+        <v>1.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="R14" t="n">
-        <v>96</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U14" t="n">
         <v>9</v>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1505,36 +1357,32 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2304.4</v>
+      </c>
       <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>16.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>52</v>
+      </c>
       <c r="O15" t="n">
-        <v>-1.14</v>
+        <v>1.43</v>
       </c>
       <c r="P15" t="n">
-        <v>2304.4</v>
+        <v>4.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="R15" t="n">
-        <v>52</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="U15" t="n">
         <v>5</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1573,46 +1421,32 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>2.73</v>
-      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>51.7</v>
+        <v>0.26</v>
       </c>
       <c r="L16" t="n">
-        <v>23.4</v>
+        <v>3567.1</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>63.77</v>
+      </c>
+      <c r="N16" t="n">
+        <v>82</v>
+      </c>
       <c r="O16" t="n">
-        <v>0.26</v>
+        <v>8.27</v>
       </c>
       <c r="P16" t="n">
-        <v>3567.1</v>
+        <v>0.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>63.77</v>
-      </c>
-      <c r="R16" t="n">
-        <v>82</v>
-      </c>
-      <c r="S16" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="U16" t="n">
         <v>-33.5</v>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1647,36 +1481,32 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2227.6</v>
+      </c>
       <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>589.23</v>
+      </c>
+      <c r="N17" t="n">
+        <v>96</v>
+      </c>
       <c r="O17" t="n">
-        <v>9.07</v>
+        <v>4.48</v>
       </c>
       <c r="P17" t="n">
-        <v>2227.6</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>589.23</v>
-      </c>
-      <c r="R17" t="n">
-        <v>96</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
         <v>17.7</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1715,36 +1545,32 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>-11.39</v>
+      </c>
+      <c r="L18" t="n">
+        <v>546.8</v>
+      </c>
       <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>18.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>91</v>
+      </c>
       <c r="O18" t="n">
-        <v>-11.39</v>
+        <v>7.25</v>
       </c>
       <c r="P18" t="n">
-        <v>546.8</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="R18" t="n">
-        <v>91</v>
-      </c>
-      <c r="S18" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
         <v>175.8</v>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1783,36 +1609,32 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3310.3</v>
+      </c>
       <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>22.29</v>
+      </c>
+      <c r="N19" t="n">
+        <v>97</v>
+      </c>
       <c r="O19" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>3310.3</v>
+        <v>4.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="R19" t="n">
-        <v>97</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="U19" t="n">
         <v>9.4</v>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1851,36 +1673,32 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1889</v>
+      </c>
       <c r="M20" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
+        <v>14.17</v>
+      </c>
+      <c r="N20" t="n">
+        <v>62</v>
+      </c>
       <c r="O20" t="n">
-        <v>-0.89</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1889</v>
+        <v>3.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="R20" t="n">
-        <v>62</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U20" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1919,36 +1737,32 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L21" t="n">
+        <v>626.7</v>
+      </c>
       <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
+        <v>86.45999999999999</v>
+      </c>
+      <c r="N21" t="n">
+        <v>66</v>
+      </c>
       <c r="O21" t="n">
-        <v>0.36</v>
+        <v>6.57</v>
       </c>
       <c r="P21" t="n">
-        <v>626.7</v>
+        <v>0.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>86.45999999999999</v>
-      </c>
-      <c r="R21" t="n">
-        <v>66</v>
-      </c>
-      <c r="S21" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U21" t="n">
         <v>31.6</v>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1987,36 +1801,32 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1675</v>
+      </c>
       <c r="M22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
+        <v>27.19</v>
+      </c>
+      <c r="N22" t="n">
+        <v>61</v>
+      </c>
       <c r="O22" t="n">
-        <v>0.93</v>
+        <v>1.02</v>
       </c>
       <c r="P22" t="n">
-        <v>1675</v>
+        <v>1.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>27.19</v>
-      </c>
-      <c r="R22" t="n">
-        <v>61</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U22" t="n">
         <v>11.1</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -2055,36 +1865,32 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1715.8</v>
+      </c>
       <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>30.21</v>
+      </c>
+      <c r="N23" t="n">
+        <v>90</v>
+      </c>
       <c r="O23" t="n">
-        <v>0.7</v>
+        <v>1.95</v>
       </c>
       <c r="P23" t="n">
-        <v>1715.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>30.21</v>
-      </c>
-      <c r="R23" t="n">
-        <v>90</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U23" t="n">
         <v>10.6</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -2105,27 +1911,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -2376,37 +2182,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>是否0050</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -5717,27 +5523,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -7854,111 +7660,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>OTC市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>未來估值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>PEG</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ForwardPE</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>成長率g%</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -7997,33 +7783,29 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21</v>
+      </c>
       <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7</v>
+      </c>
       <c r="O2" t="n">
-        <v>0.92</v>
+        <v>2.24</v>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>56</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T2" t="n">
         <v>58.3</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8062,33 +7844,29 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20.19</v>
+      </c>
       <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.02</v>
+      </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>4.43</v>
       </c>
       <c r="P3" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>72</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="T3" t="n">
         <v>10.3</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8127,33 +7905,29 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L4" t="n">
+        <v>35.84</v>
+      </c>
       <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.82</v>
+      </c>
       <c r="O4" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>35.84</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>40</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T4" t="n">
         <v>37</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8192,33 +7966,29 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L5" t="n">
+        <v>27.9</v>
+      </c>
       <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8.57</v>
+      </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>2.79</v>
       </c>
       <c r="P5" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>91</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="T5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8226,139 +7996,121 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>210.6</v>
+        <v>298.9</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1.27</v>
-      </c>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>15.1</v>
+        <v>1.85</v>
       </c>
       <c r="L6" t="n">
-        <v>13.5</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6.29</v>
+      </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>55</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>605.5</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>298.9</v>
+        <v>210.6</v>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L7" t="n">
+        <v>17.12</v>
+      </c>
       <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.39</v>
+      </c>
       <c r="O7" t="n">
-        <v>1.85</v>
+        <v>4.45</v>
       </c>
       <c r="P7" t="n">
-        <v>94.79000000000001</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>85</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>605.5</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -8393,43 +8145,29 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1.03</v>
-      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>38.8</v>
+        <v>1.15</v>
       </c>
       <c r="L8" t="n">
-        <v>60</v>
+        <v>62.01</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="N8" t="n">
+        <v>32.45</v>
+      </c>
       <c r="O8" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>83</v>
-      </c>
-      <c r="R8" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T8" t="n">
         <v>99.3</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8464,33 +8202,29 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.62</v>
+      </c>
       <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.98</v>
+      </c>
       <c r="O9" t="n">
-        <v>0.01</v>
+        <v>6.03</v>
       </c>
       <c r="P9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="S9" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="T9" t="n">
         <v>8.1</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8529,43 +8263,29 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>3.69</v>
-      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>26.3</v>
+        <v>1.13</v>
       </c>
       <c r="L10" t="n">
-        <v>7.7</v>
+        <v>28.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="N10" t="n">
+        <v>17.29</v>
+      </c>
       <c r="O10" t="n">
-        <v>1.13</v>
+        <v>3.21</v>
       </c>
       <c r="P10" t="n">
-        <v>28.33</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>74</v>
-      </c>
-      <c r="R10" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="T10" t="n">
         <v>23.8</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8600,41 +8320,29 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
+      <c r="I11" t="n">
+        <v>2</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>1.67</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.7</v>
+        <v>33.95</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.37</v>
+      </c>
       <c r="O11" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="P11" t="n">
-        <v>33.95</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>100</v>
-      </c>
-      <c r="R11" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T11" t="n">
         <v>22.1</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8669,33 +8377,29 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.01</v>
+      </c>
       <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.14</v>
+      </c>
       <c r="O12" t="n">
-        <v>2.14</v>
+        <v>1.51</v>
       </c>
       <c r="P12" t="n">
-        <v>58.01</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>100</v>
-      </c>
-      <c r="R12" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T12" t="n">
         <v>11.8</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8734,33 +8438,29 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L13" t="n">
+        <v>25.88</v>
+      </c>
       <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.6</v>
+      </c>
       <c r="O13" t="n">
-        <v>0.92</v>
+        <v>2.72</v>
       </c>
       <c r="P13" t="n">
-        <v>25.88</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>100</v>
-      </c>
-      <c r="R13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T13" t="n">
         <v>81.7</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8799,33 +8499,29 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L14" t="n">
+        <v>64.42</v>
+      </c>
       <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9.17</v>
+      </c>
       <c r="O14" t="n">
-        <v>0.68</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>64.42</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>71</v>
-      </c>
-      <c r="R14" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T14" t="n">
         <v>-43.4</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8833,23 +8529,23 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>208.6</v>
+        <v>299.1</v>
       </c>
       <c r="E15" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -8857,70 +8553,60 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>🟢未來便宜</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>2.52</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>14.7</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>6.2</v>
+        <v>127.5</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.13</v>
+      </c>
       <c r="O15" t="n">
-        <v>-0.87</v>
+        <v>0.65</v>
       </c>
       <c r="P15" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
+        <v>6.1</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>299.1</v>
+        <v>288.3</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -8928,40 +8614,36 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L16" t="n">
+        <v>70.13</v>
+      </c>
       <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.07</v>
+      </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>0.59</v>
       </c>
       <c r="P16" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>100</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="U16" t="inlineStr">
+        <v>-17.5</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8969,20 +8651,20 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>288.3</v>
+        <v>217.4</v>
       </c>
       <c r="E17" t="n">
         <v>38</v>
@@ -8993,40 +8675,36 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40.16</v>
+      </c>
       <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.01</v>
+      </c>
       <c r="O17" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="P17" t="n">
-        <v>70.13</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>79</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="U17" t="inlineStr">
+        <v>26.9</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -9034,23 +8712,23 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>217.4</v>
+        <v>208.6</v>
       </c>
       <c r="E18" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -9058,44 +8736,36 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="L18" t="n">
+        <v>15.6</v>
+      </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>3.33</v>
+      </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>5.48</v>
       </c>
       <c r="P18" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>97</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T18" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>-4.3</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9130,33 +8800,29 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="L19" t="n">
+        <v>251.19</v>
+      </c>
       <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>93</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.4</v>
+      </c>
       <c r="O19" t="n">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>251.19</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>93</v>
-      </c>
-      <c r="R19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
         <v>140.2</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -9195,33 +8861,29 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="L20" t="n">
+        <v>65.81999999999999</v>
+      </c>
       <c r="M20" t="n">
+        <v>52</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>-0.67</v>
-      </c>
       <c r="P20" t="n">
-        <v>65.81999999999999</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>52</v>
-      </c>
-      <c r="R20" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
         <v>-13.9</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -9242,27 +8904,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -9766,27 +9428,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>收盤</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -11907,32 +11569,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>轉上市定位</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>在我們PICKS</t>
         </is>
@@ -12289,12 +11951,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>值</t>
         </is>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,50 +479,70 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>未來估值</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ForwardPE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>成長率g%</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>市值(億)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -530,147 +550,171 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2429</v>
+        <v>0.1883</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.92</v>
+      </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>21.2</v>
       </c>
       <c r="L2" t="n">
-        <v>4027</v>
+        <v>29.8</v>
       </c>
       <c r="M2" t="n">
-        <v>65.19</v>
-      </c>
-      <c r="N2" t="n">
-        <v>59</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>11.44</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>0.25</v>
+        <v>2974.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>27.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U2" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1883</v>
+        <v>0.1514</v>
       </c>
       <c r="E3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2439.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="R3" t="n">
+        <v>96</v>
+      </c>
+      <c r="S3" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="U3" t="n">
         <v>85</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2974.9</v>
-      </c>
-      <c r="M3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2331</v>
+        <v>0.127</v>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -678,120 +722,138 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4</v>
+      </c>
       <c r="K4" t="n">
-        <v>1.62</v>
+        <v>14.2</v>
       </c>
       <c r="L4" t="n">
-        <v>3092.8</v>
+        <v>54.3</v>
       </c>
       <c r="M4" t="n">
-        <v>45.77</v>
-      </c>
-      <c r="N4" t="n">
-        <v>97</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>6.6</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>1.08</v>
+        <v>1863.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>21.89</v>
+      </c>
+      <c r="R4" t="n">
+        <v>74</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U4" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1514</v>
+        <v>0.2429</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2439.5</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>23.77</v>
-      </c>
-      <c r="N5" t="n">
-        <v>96</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>16.81</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.13</v>
+        <v>4027</v>
       </c>
       <c r="Q5" t="n">
-        <v>85</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>65.19</v>
+      </c>
+      <c r="R5" t="n">
+        <v>59</v>
+      </c>
+      <c r="S5" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.127</v>
+        <v>0.2331</v>
       </c>
       <c r="E6" t="n">
         <v>78</v>
@@ -802,59 +864,67 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1863.4</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="N6" t="n">
-        <v>74</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>8.51</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
-        <v>2.91</v>
+        <v>3092.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>45.77</v>
+      </c>
+      <c r="R6" t="n">
+        <v>97</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="U6" t="n">
+        <v>13</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1925</v>
+        <v>0.1732</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -866,179 +936,211 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1.35</v>
+      </c>
       <c r="K7" t="n">
-        <v>0.98</v>
+        <v>21.3</v>
       </c>
       <c r="L7" t="n">
-        <v>2750</v>
+        <v>18.7</v>
       </c>
       <c r="M7" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>66</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>5.41</v>
+        <v>1.09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2371.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>25.23</v>
+      </c>
+      <c r="R7" t="n">
+        <v>72</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="U7" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2147</v>
+        <v>0.1925</v>
       </c>
       <c r="E8" t="n">
+        <v>75</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>73</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>84</v>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3.06</v>
+      </c>
       <c r="K8" t="n">
-        <v>0.63</v>
+        <v>27.4</v>
       </c>
       <c r="L8" t="n">
-        <v>3409.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>192.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>98</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>52.47</v>
+        <v>0.98</v>
       </c>
       <c r="P8" t="n">
-        <v>0.53</v>
+        <v>2750</v>
       </c>
       <c r="Q8" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>30.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>66</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2285</v>
+        <v>0.2147</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3895.6</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>27.34</v>
-      </c>
-      <c r="N9" t="n">
-        <v>95</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>4.06</v>
+        <v>0.63</v>
       </c>
       <c r="P9" t="n">
-        <v>3.53</v>
+        <v>3409.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
+        <v>192.04</v>
+      </c>
+      <c r="R9" t="n">
+        <v>98</v>
+      </c>
+      <c r="S9" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="U9" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1732</v>
+        <v>0.2285</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1046,39 +1148,53 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M10" t="n">
         <v>3</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2371.3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="N10" t="n">
-        <v>72</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>3.23</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>3.03</v>
+        <v>3895.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>27.34</v>
+      </c>
+      <c r="R10" t="n">
+        <v>95</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="U10" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1113,32 +1229,36 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>2855.6</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>15.52</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>68</v>
       </c>
-      <c r="O11" t="n">
+      <c r="S11" t="n">
         <v>2.53</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
         <v>3.47</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="U11" t="n">
         <v>152.7</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1177,32 +1297,46 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K12" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>1.12</v>
       </c>
-      <c r="L12" t="n">
+      <c r="P12" t="n">
         <v>2625</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
         <v>57.11</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
         <v>84</v>
       </c>
-      <c r="O12" t="n">
+      <c r="S12" t="n">
         <v>31.86</v>
       </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="U12" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1237,32 +1371,44 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>2</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
         <v>2.01</v>
       </c>
-      <c r="L13" t="n">
+      <c r="P13" t="n">
         <v>2778.5</v>
       </c>
-      <c r="M13" t="n">
+      <c r="Q13" t="n">
         <v>43.57</v>
       </c>
-      <c r="N13" t="n">
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="O13" t="n">
+      <c r="S13" t="n">
         <v>4.63</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
         <v>1.23</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="U13" t="n">
         <v>30.2</v>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1297,32 +1443,46 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K14" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>0.89</v>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>2515.2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>31.35</v>
       </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>96</v>
       </c>
-      <c r="O14" t="n">
+      <c r="S14" t="n">
         <v>5.98</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="U14" t="n">
         <v>9</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1357,32 +1517,36 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
         <v>-1.14</v>
       </c>
-      <c r="L15" t="n">
+      <c r="P15" t="n">
         <v>2304.4</v>
       </c>
-      <c r="M15" t="n">
+      <c r="Q15" t="n">
         <v>16.07</v>
       </c>
-      <c r="N15" t="n">
+      <c r="R15" t="n">
         <v>52</v>
       </c>
-      <c r="O15" t="n">
+      <c r="S15" t="n">
         <v>1.43</v>
       </c>
-      <c r="P15" t="n">
+      <c r="T15" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="U15" t="n">
         <v>5</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1421,32 +1585,46 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K16" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
         <v>0.26</v>
       </c>
-      <c r="L16" t="n">
+      <c r="P16" t="n">
         <v>3567.1</v>
       </c>
-      <c r="M16" t="n">
+      <c r="Q16" t="n">
         <v>63.77</v>
       </c>
-      <c r="N16" t="n">
+      <c r="R16" t="n">
         <v>82</v>
       </c>
-      <c r="O16" t="n">
+      <c r="S16" t="n">
         <v>8.27</v>
       </c>
-      <c r="P16" t="n">
+      <c r="T16" t="n">
         <v>0.78</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="U16" t="n">
         <v>-33.5</v>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1481,32 +1659,36 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
         <v>9.07</v>
       </c>
-      <c r="L17" t="n">
+      <c r="P17" t="n">
         <v>2227.6</v>
       </c>
-      <c r="M17" t="n">
+      <c r="Q17" t="n">
         <v>589.23</v>
       </c>
-      <c r="N17" t="n">
+      <c r="R17" t="n">
         <v>96</v>
       </c>
-      <c r="O17" t="n">
+      <c r="S17" t="n">
         <v>4.48</v>
       </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="U17" t="n">
         <v>17.7</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1545,32 +1727,36 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
         <v>-11.39</v>
       </c>
-      <c r="L18" t="n">
+      <c r="P18" t="n">
         <v>546.8</v>
       </c>
-      <c r="M18" t="n">
+      <c r="Q18" t="n">
         <v>18.01</v>
       </c>
-      <c r="N18" t="n">
+      <c r="R18" t="n">
         <v>91</v>
       </c>
-      <c r="O18" t="n">
+      <c r="S18" t="n">
         <v>7.25</v>
       </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="U18" t="n">
         <v>175.8</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1609,32 +1795,36 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
         <v>1.01</v>
       </c>
-      <c r="L19" t="n">
+      <c r="P19" t="n">
         <v>3310.3</v>
       </c>
-      <c r="M19" t="n">
+      <c r="Q19" t="n">
         <v>22.29</v>
       </c>
-      <c r="N19" t="n">
+      <c r="R19" t="n">
         <v>97</v>
       </c>
-      <c r="O19" t="n">
+      <c r="S19" t="n">
         <v>4.6</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
         <v>4.23</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="U19" t="n">
         <v>9.4</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1673,32 +1863,36 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>3</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
         <v>-0.89</v>
       </c>
-      <c r="L20" t="n">
+      <c r="P20" t="n">
         <v>1889</v>
       </c>
-      <c r="M20" t="n">
+      <c r="Q20" t="n">
         <v>14.17</v>
       </c>
-      <c r="N20" t="n">
+      <c r="R20" t="n">
         <v>62</v>
       </c>
-      <c r="O20" t="n">
+      <c r="S20" t="n">
         <v>2.1</v>
       </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="U20" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1737,32 +1931,36 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
         <v>0.36</v>
       </c>
-      <c r="L21" t="n">
+      <c r="P21" t="n">
         <v>626.7</v>
       </c>
-      <c r="M21" t="n">
+      <c r="Q21" t="n">
         <v>86.45999999999999</v>
       </c>
-      <c r="N21" t="n">
+      <c r="R21" t="n">
         <v>66</v>
       </c>
-      <c r="O21" t="n">
+      <c r="S21" t="n">
         <v>6.57</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="U21" t="n">
         <v>31.6</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1801,32 +1999,36 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>2</v>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
         <v>0.93</v>
       </c>
-      <c r="L22" t="n">
+      <c r="P22" t="n">
         <v>1675</v>
       </c>
-      <c r="M22" t="n">
+      <c r="Q22" t="n">
         <v>27.19</v>
       </c>
-      <c r="N22" t="n">
+      <c r="R22" t="n">
         <v>61</v>
       </c>
-      <c r="O22" t="n">
+      <c r="S22" t="n">
         <v>1.02</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>1.32</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="U22" t="n">
         <v>11.1</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1865,32 +2067,36 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
         <v>0.7</v>
       </c>
-      <c r="L23" t="n">
+      <c r="P23" t="n">
         <v>1715.8</v>
       </c>
-      <c r="M23" t="n">
+      <c r="Q23" t="n">
         <v>30.21</v>
       </c>
-      <c r="N23" t="n">
+      <c r="R23" t="n">
         <v>90</v>
       </c>
-      <c r="O23" t="n">
+      <c r="S23" t="n">
         <v>1.95</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
         <v>2.86</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="U23" t="n">
         <v>10.6</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7660,7 +7866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7706,45 +7912,65 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>未來估值</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ForwardPE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>成長率g%</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -7783,29 +8009,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>0.92</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>21</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>56</v>
       </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
         <v>7</v>
       </c>
-      <c r="O2" t="n">
+      <c r="S2" t="n">
         <v>2.24</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
         <v>58.3</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7844,29 +8074,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>1.53</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>20.19</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>72</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>3.02</v>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
         <v>4.43</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7905,29 +8139,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>1.85</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>35.84</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>40</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>3.82</v>
       </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
         <v>1.05</v>
       </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
         <v>37</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7966,29 +8204,33 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>1.21</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>27.9</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>91</v>
       </c>
-      <c r="N5" t="n">
+      <c r="R5" t="n">
         <v>8.57</v>
       </c>
-      <c r="O5" t="n">
+      <c r="S5" t="n">
         <v>2.79</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
         <v>15.4</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7996,121 +8238,139 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>298.9</v>
+        <v>210.6</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🟡未來合理</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M6" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="L6" t="n">
-        <v>94.79000000000001</v>
-      </c>
-      <c r="M6" t="n">
-        <v>85</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6.29</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>605.5</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>17.12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>55</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>210.6</v>
+        <v>298.9</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="L7" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="M7" t="n">
-        <v>55</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.39</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>4.45</v>
+        <v>1.85</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>94.79000000000001</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>85</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>605.5</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -8145,29 +8405,43 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K8" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>60</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>1.15</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>62.01</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>83</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>32.45</v>
       </c>
-      <c r="O8" t="n">
+      <c r="S8" t="n">
         <v>1.09</v>
       </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
         <v>99.3</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8202,29 +8476,33 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>0.01</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>2.62</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
         <v>0.98</v>
       </c>
-      <c r="O9" t="n">
+      <c r="S9" t="n">
         <v>6.03</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
         <v>8.1</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8263,29 +8541,43 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M10" t="n">
         <v>3</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>1.13</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>28.33</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>74</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>17.29</v>
       </c>
-      <c r="O10" t="n">
+      <c r="S10" t="n">
         <v>3.21</v>
       </c>
-      <c r="P10" t="n">
+      <c r="T10" t="n">
         <v>23.8</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8320,29 +8612,41 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>2</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
+        <v>36</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>1.67</v>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>33.95</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>100</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>4.37</v>
       </c>
-      <c r="O11" t="n">
+      <c r="S11" t="n">
         <v>2.12</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
         <v>22.1</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8377,29 +8681,33 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>2.14</v>
       </c>
-      <c r="L12" t="n">
+      <c r="P12" t="n">
         <v>58.01</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
         <v>4.14</v>
       </c>
-      <c r="O12" t="n">
+      <c r="S12" t="n">
         <v>1.51</v>
       </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8438,29 +8746,33 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
         <v>0.92</v>
       </c>
-      <c r="L13" t="n">
+      <c r="P13" t="n">
         <v>25.88</v>
       </c>
-      <c r="M13" t="n">
+      <c r="Q13" t="n">
         <v>100</v>
       </c>
-      <c r="N13" t="n">
+      <c r="R13" t="n">
         <v>5.6</v>
       </c>
-      <c r="O13" t="n">
+      <c r="S13" t="n">
         <v>2.72</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
         <v>81.7</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8499,29 +8811,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>0.68</v>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>64.42</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>71</v>
       </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>9.17</v>
       </c>
-      <c r="O14" t="n">
+      <c r="S14" t="n">
         <v>1.43</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
         <v>-43.4</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8529,23 +8845,23 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>299.1</v>
+        <v>208.6</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -8553,60 +8869,70 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2.52</v>
+      </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>14.7</v>
       </c>
       <c r="L15" t="n">
-        <v>127.5</v>
+        <v>6.2</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.13</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>0.65</v>
+        <v>-0.87</v>
       </c>
       <c r="P15" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>288.3</v>
+        <v>299.1</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -8614,36 +8940,40 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="L16" t="n">
-        <v>70.13</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>79</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.07</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>0.59</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+        <v>127.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>100</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8651,20 +8981,20 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>217.4</v>
+        <v>288.3</v>
       </c>
       <c r="E17" t="n">
         <v>38</v>
@@ -8675,36 +9005,40 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="M17" t="n">
-        <v>97</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.01</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+        <v>70.13</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>79</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8712,23 +9046,23 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>208.6</v>
+        <v>217.4</v>
       </c>
       <c r="E18" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -8736,36 +9070,44 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="L18" t="n">
-        <v>15.6</v>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.33</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>5.48</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>40.16</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>97</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T18" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8800,29 +9142,33 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
         <v>-3.66</v>
       </c>
-      <c r="L19" t="n">
+      <c r="P19" t="n">
         <v>251.19</v>
       </c>
-      <c r="M19" t="n">
+      <c r="Q19" t="n">
         <v>93</v>
       </c>
-      <c r="N19" t="n">
+      <c r="R19" t="n">
         <v>9.4</v>
       </c>
-      <c r="O19" t="n">
+      <c r="S19" t="n">
         <v>0</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
         <v>140.2</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8861,29 +9207,33 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
         <v>-0.67</v>
       </c>
-      <c r="L20" t="n">
+      <c r="P20" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="M20" t="n">
+      <c r="Q20" t="n">
         <v>52</v>
       </c>
-      <c r="N20" t="n">
+      <c r="R20" t="n">
         <v>8.01</v>
       </c>
-      <c r="O20" t="n">
+      <c r="S20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
         <v>-13.9</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -803,7 +803,11 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -871,7 +875,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -932,7 +940,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1087,7 +1095,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1222,14 +1234,18 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1373,16 +1389,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 成長為負(-16%)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-16.5</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2</v>
       </c>
@@ -1517,7 +1529,11 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1659,7 +1675,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1727,7 +1747,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1788,14 +1812,18 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1856,14 +1884,18 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1931,7 +1963,11 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1999,7 +2035,11 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -2067,7 +2107,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -2572,7 +2616,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4139,7 +4183,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8009,7 +8053,11 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -8074,7 +8122,11 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -8139,7 +8191,11 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -8204,7 +8260,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -8340,7 +8400,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -8476,7 +8540,11 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -8614,16 +8682,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 成長為負(-6%)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>36</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-5.7</v>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2</v>
       </c>
@@ -8681,7 +8745,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -8746,7 +8814,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -8811,7 +8883,11 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -8947,7 +9023,11 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -9012,7 +9092,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -9070,14 +9154,18 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -9142,7 +9230,11 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -9207,7 +9299,11 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,50 +499,55 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>⑪動態惡化扣分</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>市值(億)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -596,48 +601,51 @@
         <v>29.8</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>4</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>1.13</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>2974.9</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>27.5</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>100</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>5.1</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>2.24</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>46.6</v>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1514</v>
+        <v>0.127</v>
       </c>
       <c r="E3" t="n">
         <v>98</v>
@@ -648,7 +656,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -661,60 +669,63 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.61</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>17.1</v>
+        <v>14.2</v>
       </c>
       <c r="L3" t="n">
-        <v>39.2</v>
+        <v>54.3</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>3</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>2.64</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>2439.5</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.77</v>
+        <v>1863.4</v>
       </c>
       <c r="R3" t="n">
-        <v>96</v>
+        <v>21.89</v>
       </c>
       <c r="S3" t="n">
-        <v>16.81</v>
+        <v>74</v>
       </c>
       <c r="T3" t="n">
-        <v>3.13</v>
+        <v>8.51</v>
       </c>
       <c r="U3" t="n">
-        <v>85</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
+        <v>2.91</v>
+      </c>
+      <c r="V3" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.127</v>
+        <v>0.1514</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>90.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -722,7 +733,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -735,40 +746,43 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="K4" t="n">
-        <v>14.2</v>
+        <v>17.1</v>
       </c>
       <c r="L4" t="n">
-        <v>54.3</v>
+        <v>39.2</v>
       </c>
       <c r="M4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N4" t="n">
         <v>3</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>1.56</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1863.4</v>
+        <v>2.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.89</v>
+        <v>2439.5</v>
       </c>
       <c r="R4" t="n">
-        <v>74</v>
+        <v>23.77</v>
       </c>
       <c r="S4" t="n">
-        <v>8.51</v>
+        <v>96</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>16.81</v>
       </c>
       <c r="U4" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>3.13</v>
+      </c>
+      <c r="V4" t="n">
+        <v>85</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -812,31 +826,34 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>2</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>4027</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>65.19</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>59</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>11.44</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>0.25</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>108.5</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -884,31 +901,34 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>1.62</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3092.8</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>45.77</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>97</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>6.6</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1.08</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>13</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -916,23 +936,23 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1732</v>
+        <v>0.1925</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -940,155 +960,159 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.35</v>
+        <v>3.06</v>
       </c>
       <c r="K7" t="n">
-        <v>21.3</v>
+        <v>27.4</v>
       </c>
       <c r="L7" t="n">
-        <v>18.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>1.09</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>2371.3</v>
+        <v>0.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.23</v>
+        <v>2750</v>
       </c>
       <c r="R7" t="n">
-        <v>72</v>
+        <v>30.1</v>
       </c>
       <c r="S7" t="n">
-        <v>3.23</v>
+        <v>66</v>
       </c>
       <c r="T7" t="n">
-        <v>3.03</v>
+        <v>5.41</v>
       </c>
       <c r="U7" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
+        <v>2.12</v>
+      </c>
+      <c r="V7" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1925</v>
+        <v>0.2147</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="K8" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>9.800000000000001</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>0.98</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>2750</v>
+        <v>0.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>30.1</v>
+        <v>3409.2</v>
       </c>
       <c r="R8" t="n">
-        <v>66</v>
+        <v>192.04</v>
       </c>
       <c r="S8" t="n">
-        <v>5.41</v>
+        <v>98</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>52.47</v>
       </c>
       <c r="U8" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
+        <v>0.53</v>
+      </c>
+      <c r="V8" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2147</v>
+        <v>0.2285</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1097,62 +1121,67 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>0.63</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>3409.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>192.04</v>
+        <v>3895.6</v>
       </c>
       <c r="R9" t="n">
-        <v>98</v>
+        <v>27.34</v>
       </c>
       <c r="S9" t="n">
-        <v>52.47</v>
+        <v>95</v>
       </c>
       <c r="T9" t="n">
-        <v>0.53</v>
+        <v>4.06</v>
       </c>
       <c r="U9" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>3.53</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2285</v>
+        <v>0.1732</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>70.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1160,7 +1189,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1169,72 +1198,75 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>4.94</v>
+        <v>1.35</v>
       </c>
       <c r="K10" t="n">
-        <v>25.9</v>
+        <v>21.3</v>
       </c>
       <c r="L10" t="n">
-        <v>5.5</v>
+        <v>18.7</v>
       </c>
       <c r="M10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>3895.6</v>
+        <v>1.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.34</v>
+        <v>2371.3</v>
       </c>
       <c r="R10" t="n">
-        <v>95</v>
+        <v>25.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4.06</v>
+        <v>72</v>
       </c>
       <c r="T10" t="n">
-        <v>3.53</v>
+        <v>3.23</v>
       </c>
       <c r="U10" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
+        <v>3.03</v>
+      </c>
+      <c r="V10" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.251</v>
+        <v>0.1898</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1243,70 +1275,75 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K11" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>20.2</v>
+      </c>
       <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>-0.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>2855.6</v>
+        <v>1.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.52</v>
+        <v>2625</v>
       </c>
       <c r="R11" t="n">
-        <v>68</v>
+        <v>57.11</v>
       </c>
       <c r="S11" t="n">
-        <v>2.53</v>
+        <v>84</v>
       </c>
       <c r="T11" t="n">
-        <v>3.47</v>
+        <v>31.86</v>
       </c>
       <c r="U11" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>1.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1898</v>
+        <v>0.1978</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1315,72 +1352,69 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="K12" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>20.2</v>
-      </c>
+          <t>⏸ 成長為負(-16%)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>1.12</v>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>2625</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>57.11</v>
+        <v>2778.5</v>
       </c>
       <c r="R12" t="n">
-        <v>84</v>
+        <v>43.57</v>
       </c>
       <c r="S12" t="n">
-        <v>31.86</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>1.44</v>
+        <v>4.63</v>
       </c>
       <c r="U12" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="V12" t="inlineStr"/>
+        <v>1.23</v>
+      </c>
+      <c r="V12" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1978</v>
+        <v>0.251</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>57.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1389,38 +1423,45 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-16%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>2.01</v>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>2778.5</v>
+        <v>-0.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>43.57</v>
+        <v>2855.6</v>
       </c>
       <c r="R13" t="n">
-        <v>100</v>
+        <v>15.52</v>
       </c>
       <c r="S13" t="n">
-        <v>4.63</v>
+        <v>68</v>
       </c>
       <c r="T13" t="n">
-        <v>1.23</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V13" t="inlineStr"/>
+        <v>3.47</v>
+      </c>
+      <c r="V13" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1472,29 +1513,32 @@
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>0.89</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>2515.2</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>31.35</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>96</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>5.98</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>1.57</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>9</v>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1538,31 +1582,34 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>-1.14</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>2304.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>16.07</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>52</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>1.43</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>4.99</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>5</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1616,31 +1663,34 @@
         <v>23.4</v>
       </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>2</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>0.26</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3567.1</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>63.77</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>82</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>8.27</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>0.78</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>-33.5</v>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1684,31 +1734,34 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>9.07</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>2227.6</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>589.23</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>96</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>4.48</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>0</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>17.7</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1756,31 +1809,34 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>-11.39</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>546.8</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>18.01</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>91</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>7.25</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>0</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>175.8</v>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1788,23 +1844,23 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1996</v>
+        <v>0.1605</v>
       </c>
       <c r="E19" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1812,7 +1868,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1828,31 +1884,34 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>1.01</v>
-      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>3310.3</v>
+        <v>0.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.29</v>
+        <v>626.7</v>
       </c>
       <c r="R19" t="n">
-        <v>97</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>4.6</v>
+        <v>66</v>
       </c>
       <c r="T19" t="n">
-        <v>4.23</v>
+        <v>6.57</v>
       </c>
       <c r="U19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="V19" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1876,7 +1935,7 @@
         <v>0.1357</v>
       </c>
       <c r="E20" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1900,31 +1959,34 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>-0.89</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>1889</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>14.17</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>62</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>2.1</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>3.38</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1932,23 +1994,23 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1605</v>
+        <v>0.1996</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1956,7 +2018,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1972,31 +2034,34 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
+        <v>-10</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0.36</v>
-      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>626.7</v>
+        <v>1.01</v>
       </c>
       <c r="Q21" t="n">
-        <v>86.45999999999999</v>
+        <v>3310.3</v>
       </c>
       <c r="R21" t="n">
-        <v>66</v>
+        <v>22.29</v>
       </c>
       <c r="S21" t="n">
-        <v>6.57</v>
+        <v>97</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="U21" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="V21" t="inlineStr">
+        <v>4.23</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -2044,31 +2109,34 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>2</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>0.93</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>1675</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>27.19</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>61</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>1.02</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>1.32</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>11.1</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -2116,31 +2184,34 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>2</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>0.7</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>1715.8</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>30.21</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>90</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>1.95</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>2.86</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>10.6</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7910,7 +7981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7976,45 +8047,50 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>⑪動態惡化扣分</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -8062,28 +8138,31 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>3</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>0.92</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>21</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>56</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>2.24</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>58.3</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8131,28 +8210,31 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>3</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>1.53</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>20.19</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>72</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>3.02</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>4.43</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>10.3</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8200,28 +8282,31 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>4</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>1.85</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>35.84</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>40</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>3.82</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1.05</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>37</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8269,28 +8354,31 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>1.21</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>27.9</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>91</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>8.57</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>2.79</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8344,28 +8432,31 @@
         <v>13.5</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>3</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>1.28</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>17.12</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>55</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>3.39</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>4.45</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>0.6</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8409,28 +8500,31 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>3</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>1.85</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>94.79000000000001</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>85</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>6.29</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>605.5</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8484,28 +8578,31 @@
         <v>60</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>3</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>1.15</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>62.01</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>83</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>32.45</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>1.09</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>99.3</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8549,28 +8646,31 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>0.01</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>0.98</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>6.03</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>8.1</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8624,28 +8724,31 @@
         <v>7.7</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>1.13</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>28.33</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>74</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>17.29</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>3.21</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>23.8</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8689,28 +8792,31 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>1.67</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>33.95</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>100</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>4.37</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>2.12</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>22.1</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8754,28 +8860,31 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>2.14</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>58.01</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>4.14</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1.51</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>11.8</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8823,28 +8932,31 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>0.92</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>25.88</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>2.72</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>81.7</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8892,28 +9004,31 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>0.68</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>64.42</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>71</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>9.17</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1.43</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>-43.4</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -8967,28 +9082,31 @@
         <v>6.2</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>2</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>-0.87</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>3.33</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>5.48</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9034,26 +9152,29 @@
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>3.75</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>127.5</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>100</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>1.13</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>0.65</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>6.1</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -9101,28 +9222,31 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>1.14</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>70.13</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>79</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>7.07</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>0.59</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-17.5</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -9130,23 +9254,23 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>217.4</v>
+        <v>260.7</v>
       </c>
       <c r="E18" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -9154,7 +9278,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -9170,28 +9294,31 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>3.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>40.16</v>
+        <v>-3.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>97</v>
+        <v>251.19</v>
       </c>
       <c r="R18" t="n">
-        <v>4.01</v>
+        <v>93</v>
       </c>
       <c r="S18" t="n">
-        <v>1.48</v>
+        <v>9.4</v>
       </c>
       <c r="T18" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="U18" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -9199,23 +9326,23 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>260.7</v>
+        <v>274.2</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -9223,11 +9350,11 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9239,28 +9366,31 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>-3.66</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>251.19</v>
+        <v>-0.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>93</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>9.4</v>
+        <v>52</v>
       </c>
       <c r="S19" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="T19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="U19" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -9268,20 +9398,20 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>274.2</v>
+        <v>217.4</v>
       </c>
       <c r="E20" t="n">
         <v>23</v>
@@ -9292,11 +9422,11 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9308,28 +9438,31 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>-0.67</v>
-      </c>
+        <v>-10</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>65.81999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>52</v>
+        <v>40.16</v>
       </c>
       <c r="R20" t="n">
-        <v>8.01</v>
+        <v>97</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="U20" t="inlineStr">
+        <v>1.48</v>
+      </c>
+      <c r="U20" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="K6" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>13.5</v>
@@ -8442,16 +8442,16 @@
         <v>1.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.12</v>
+        <v>17.05</v>
       </c>
       <c r="R6" t="n">
         <v>55</v>
       </c>
       <c r="S6" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="T6" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="U6" t="n">
         <v>0.6</v>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1844,23 +1844,23 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1605</v>
+        <v>0.1632</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1887,29 +1887,29 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>0.36</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>626.7</v>
+        <v>2306.6</v>
       </c>
       <c r="R19" t="n">
-        <v>86.45999999999999</v>
+        <v>19.77</v>
       </c>
       <c r="S19" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="T19" t="n">
-        <v>6.57</v>
+        <v>1.14</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4</v>
+        <v>4.66</v>
       </c>
       <c r="V19" t="n">
-        <v>31.6</v>
+        <v>12</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -1919,23 +1919,23 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1357</v>
+        <v>0.1605</v>
       </c>
       <c r="E20" t="n">
-        <v>30.5</v>
+        <v>35</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1959,32 +1959,32 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>-0.89</v>
+        <v>0.36</v>
       </c>
       <c r="Q20" t="n">
-        <v>1889</v>
+        <v>626.7</v>
       </c>
       <c r="R20" t="n">
-        <v>14.17</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>6.57</v>
       </c>
       <c r="U20" t="n">
-        <v>3.38</v>
+        <v>0.4</v>
       </c>
       <c r="V20" t="n">
-        <v>82.90000000000001</v>
+        <v>31.6</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -1994,23 +1994,23 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1996</v>
+        <v>0.1357</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>30.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2034,32 +2034,32 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.01</v>
+        <v>-0.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>3310.3</v>
+        <v>1889</v>
       </c>
       <c r="R21" t="n">
-        <v>22.29</v>
+        <v>14.17</v>
       </c>
       <c r="S21" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="T21" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>4.23</v>
+        <v>3.38</v>
       </c>
       <c r="V21" t="n">
-        <v>9.4</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2069,20 +2069,20 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1181</v>
+        <v>0.1996</v>
       </c>
       <c r="E22" t="n">
         <v>26</v>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2109,32 +2109,32 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>1675</v>
+        <v>3310.3</v>
       </c>
       <c r="R22" t="n">
-        <v>27.19</v>
+        <v>22.29</v>
       </c>
       <c r="S22" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="T22" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>4.23</v>
       </c>
       <c r="V22" t="n">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2144,23 +2144,23 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1226</v>
+        <v>0.1181</v>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2168,11 +2168,11 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2191,27 +2191,102 @@
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1675</v>
+      </c>
+      <c r="R23" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="S23" t="n">
+        <v>61</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>88</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>36</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>1715.8</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>30.21</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>90</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>1.95</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>2.86</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>10.6</v>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -2228,7 +2303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,20 +2358,20 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1632</v>
+        <v>0.1582</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2306,20 +2381,20 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1582</v>
+        <v>0.1339</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2329,20 +2404,20 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1339</v>
+        <v>0.1331</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2352,20 +2427,20 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1331</v>
+        <v>0.1329</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2375,20 +2450,20 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1329</v>
+        <v>0.1316</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2398,20 +2473,20 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1316</v>
+        <v>0.1265</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2421,20 +2496,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1265</v>
+        <v>0.1262</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2444,45 +2519,22 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1262</v>
+        <v>0.1194</v>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>89</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.1194</v>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>加入 PICKS 抓體檢</t>
         </is>
@@ -2499,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3099,20 +3151,20 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.3992</v>
+        <v>0.408</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3121,7 +3173,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3132,25 +3184,29 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.3887</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>0.3992</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3161,29 +3217,25 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.3791</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.3887</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3194,20 +3246,20 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.3768</v>
+        <v>0.3791</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3216,7 +3268,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3227,20 +3279,20 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.3736</v>
+        <v>0.3768</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3249,7 +3301,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3260,25 +3312,29 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.3577</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>0.3736</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3289,53 +3345,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.3442</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.3577</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.3367</v>
+        <v>0.3442</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -3344,69 +3396,69 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.3319</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+        <v>0.3367</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.3226</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.3319</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3417,20 +3469,20 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.2989</v>
+        <v>0.3226</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3439,7 +3491,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3450,20 +3502,20 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.2947</v>
+        <v>0.2989</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3472,7 +3524,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3483,20 +3535,20 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.2919</v>
+        <v>0.2947</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3505,7 +3557,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3516,20 +3568,20 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2854</v>
+        <v>0.2919</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3538,69 +3590,69 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.2802</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>0.2854</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.2797</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2802</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3611,25 +3663,29 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.2641</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+        <v>0.2797</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3640,29 +3696,25 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.2626</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2641</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3673,25 +3725,29 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2577</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
+        <v>0.2626</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3702,25 +3758,25 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.251</v>
+        <v>0.2577</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3731,141 +3787,145 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.2429</v>
+        <v>0.251</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
+        <v>0.2464</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.2331</v>
+        <v>0.2429</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.2285</v>
+        <v>0.2408</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2211</v>
+        <v>0.2331</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3876,25 +3936,25 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2147</v>
+        <v>0.2285</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3905,29 +3965,25 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.2056</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2211</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3938,20 +3994,20 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.2051</v>
+        <v>0.2147</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
@@ -3967,54 +4023,58 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.1996</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
+        <v>0.2056</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.1978</v>
+        <v>0.2051</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4025,25 +4085,25 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.1925</v>
+        <v>0.1996</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4054,25 +4114,25 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.1898</v>
+        <v>0.1978</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4083,87 +4143,83 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.1883</v>
+        <v>0.1925</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.1898</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.1732</v>
+        <v>0.1883</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4174,25 +4230,29 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.1704</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>0.185</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4203,58 +4263,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.1605</v>
+        <v>0.1732</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.1704</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4265,107 +4321,111 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.1514</v>
+        <v>0.1632</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.1438</v>
+        <v>0.1605</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.1357</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>0.153</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.127</v>
+        <v>0.1514</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
@@ -4381,25 +4441,25 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.1226</v>
+        <v>0.1438</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4410,20 +4470,20 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1181</v>
+        <v>0.1357</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
@@ -4439,20 +4499,20 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.1176</v>
+        <v>0.127</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -4468,83 +4528,83 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.1001</v>
+        <v>0.1226</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.099</v>
+        <v>0.1181</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.0946</v>
+        <v>0.1176</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4555,20 +4615,20 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.0784</v>
+        <v>0.1001</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
@@ -4578,60 +4638,60 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.0764</v>
+        <v>0.099</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0757</v>
+        <v>0.0946</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4642,83 +4702,83 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0851</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0738</v>
+        <v>0.0784</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.0731</v>
+        <v>0.0774</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4729,54 +4789,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.0727</v>
+        <v>0.0764</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0693</v>
+        <v>0.0757</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4787,83 +4847,83 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0667</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0658</v>
+        <v>0.0738</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0599</v>
+        <v>0.0731</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4874,20 +4934,20 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.0576</v>
+        <v>0.0727</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
@@ -4897,31 +4957,31 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>群益證</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.0575</v>
+        <v>0.0693</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4932,25 +4992,25 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0547</v>
+        <v>0.0667</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4961,25 +5021,25 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0537</v>
+        <v>0.0658</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4990,25 +5050,25 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.0523</v>
+        <v>0.0599</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5019,25 +5079,25 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0521</v>
+        <v>0.0576</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5048,25 +5108,25 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>群益證</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.0491</v>
+        <v>0.0575</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5077,54 +5137,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0479</v>
+        <v>0.0547</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.0467</v>
+        <v>0.0537</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5135,49 +5195,49 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.0445</v>
+        <v>0.0523</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>大同</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.0441</v>
+        <v>0.0521</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
@@ -5187,26 +5247,26 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.0429</v>
+        <v>0.0499</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
@@ -5222,25 +5282,25 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.0426</v>
+        <v>0.0491</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5251,25 +5311,25 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>台灣精銳</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.0396</v>
+        <v>0.0479</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5280,20 +5340,20 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.0385</v>
+        <v>0.0467</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
@@ -5309,78 +5369,78 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.038</v>
+        <v>0.0445</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>大同</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0367</v>
+        <v>0.0441</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.0354</v>
+        <v>0.0429</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
@@ -5390,26 +5450,26 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>定穎投控</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.0338</v>
+        <v>0.0426</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
@@ -5425,20 +5485,20 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>潤泰全</t>
+          <t>台灣精銳</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.0334</v>
+        <v>0.0396</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
@@ -5448,31 +5508,31 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>531</v>
+        <v>177</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>晶彩科</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0067</v>
+        <v>0.0385</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5483,107 +5543,107 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>532</v>
+        <v>178</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.0067</v>
+        <v>0.038</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>560</v>
+        <v>180</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>國票金</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.0061</v>
+        <v>0.0367</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>584</v>
+        <v>189</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0056</v>
+        <v>0.0354</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>587</v>
+        <v>196</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>豐達科</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.0055</v>
+        <v>0.0338</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
@@ -5593,26 +5653,26 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>589</v>
+        <v>200</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>潤泰全</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.0054</v>
+        <v>0.0334</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
@@ -5622,26 +5682,26 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>590</v>
+        <v>531</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>晶彩科</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.0054</v>
+        <v>0.0067</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
@@ -5651,26 +5711,26 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>613</v>
+        <v>532</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>一零四</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.005</v>
+        <v>0.0067</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
@@ -5686,107 +5746,107 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>655</v>
+        <v>541</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.0043</v>
+        <v>0.0065</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>661</v>
+        <v>560</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>凌群</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.0042</v>
+        <v>0.0061</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>695</v>
+        <v>572</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>中鋼構</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.0037</v>
+        <v>0.0058</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>701</v>
+        <v>584</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.0036</v>
+        <v>0.0056</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
@@ -5796,26 +5856,26 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>710</v>
+        <v>587</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>豐達科</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.0035</v>
+        <v>0.0055</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
@@ -5824,6 +5884,238 @@
         </is>
       </c>
       <c r="G111" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>589</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>7730</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>暉盛-創</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>590</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>9918</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>欣天然</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>613</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>一零四</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>655</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>台耀</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>661</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>695</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>6776</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>展碁國際</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>701</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>邁達特</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>710</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>訊連</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>🟢便宜</t>
         </is>
@@ -12578,7 +12870,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -12588,7 +12880,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -12598,7 +12890,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -12608,7 +12900,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -3173,7 +3173,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,117 +425,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>市值(億)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -2307,27 +2295,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -2555,37 +2543,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>是否0050</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -6136,27 +6124,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -8277,112 +8265,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OTC市值億</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -9775,27 +9763,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -10299,27 +10287,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>收盤</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -12440,32 +12428,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>轉上市定位</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>在我們PICKS</t>
         </is>
@@ -12822,12 +12810,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>值</t>
         </is>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富櫃50候選B_blind" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OTC前100" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OTC轉上市觀察" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="門檻說明" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0050剔除警報" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="門檻說明" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,108 +544,106 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1883</v>
+        <v>0.2429</v>
       </c>
       <c r="E2" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="K2" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>29.8</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2974.9</v>
+        <v>4027</v>
       </c>
       <c r="R2" t="n">
-        <v>27.5</v>
+        <v>65.19</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="T2" t="n">
-        <v>5.1</v>
+        <v>11.44</v>
       </c>
       <c r="U2" t="n">
-        <v>2.24</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>108.5</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.127</v>
+        <v>0.2641</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -653,75 +652,73 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>54.3</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>2.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>1863.4</v>
+        <v>4194.2</v>
       </c>
       <c r="R3" t="n">
-        <v>21.89</v>
+        <v>195.58</v>
       </c>
       <c r="S3" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="T3" t="n">
-        <v>8.51</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>2.91</v>
+        <v>0.22</v>
       </c>
       <c r="V3" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1514</v>
+        <v>0.2577</v>
       </c>
       <c r="E4" t="n">
-        <v>90.5</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -730,79 +727,77 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K4" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>39.2</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>2439.5</v>
+        <v>3462.9</v>
       </c>
       <c r="R4" t="n">
-        <v>23.77</v>
+        <v>46.36</v>
       </c>
       <c r="S4" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="T4" t="n">
-        <v>16.81</v>
+        <v>3.59</v>
       </c>
       <c r="U4" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>85</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>58.9</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2429</v>
+        <v>0.2331</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -817,29 +812,29 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>4027</v>
+        <v>3092.8</v>
       </c>
       <c r="R5" t="n">
-        <v>65.19</v>
+        <v>45.77</v>
       </c>
       <c r="S5" t="n">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="T5" t="n">
-        <v>11.44</v>
+        <v>6.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0.25</v>
+        <v>1.08</v>
       </c>
       <c r="V5" t="n">
-        <v>108.5</v>
+        <v>13</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -849,23 +844,23 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2331</v>
+        <v>0.2147</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -873,7 +868,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -892,29 +887,29 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.62</v>
+        <v>0.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>3092.8</v>
+        <v>3409.2</v>
       </c>
       <c r="R6" t="n">
-        <v>45.77</v>
+        <v>192.04</v>
       </c>
       <c r="S6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="T6" t="n">
-        <v>6.6</v>
+        <v>52.47</v>
       </c>
       <c r="U6" t="n">
-        <v>1.08</v>
+        <v>0.53</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>119.8</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -924,23 +919,23 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1925</v>
+        <v>0.2285</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -948,11 +943,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -961,71 +956,71 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3.06</v>
+        <v>4.94</v>
       </c>
       <c r="K7" t="n">
-        <v>27.4</v>
+        <v>25.9</v>
       </c>
       <c r="L7" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>0.98</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2750</v>
+        <v>3895.6</v>
       </c>
       <c r="R7" t="n">
-        <v>30.1</v>
+        <v>27.34</v>
       </c>
       <c r="S7" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="T7" t="n">
-        <v>5.41</v>
+        <v>4.06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>3.53</v>
       </c>
       <c r="V7" t="n">
-        <v>40.4</v>
+        <v>13.7</v>
       </c>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2147</v>
+        <v>0.2802</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1048,25 +1043,25 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>0.63</v>
+        <v>21.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3409.2</v>
+        <v>5272.9</v>
       </c>
       <c r="R8" t="n">
-        <v>192.04</v>
+        <v>600</v>
       </c>
       <c r="S8" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T8" t="n">
-        <v>52.47</v>
+        <v>2.32</v>
       </c>
       <c r="U8" t="n">
-        <v>0.53</v>
+        <v>1.52</v>
       </c>
       <c r="V8" t="n">
-        <v>119.8</v>
+        <v>10.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1076,31 +1071,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2285</v>
+        <v>0.251</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>46.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1109,152 +1104,150 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="K9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.5</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3895.6</v>
+        <v>2855.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.34</v>
+        <v>15.52</v>
       </c>
       <c r="S9" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="T9" t="n">
-        <v>4.06</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>3.53</v>
+        <v>3.47</v>
       </c>
       <c r="V9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>152.7</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1732</v>
+        <v>0.2408</v>
       </c>
       <c r="E10" t="n">
-        <v>70.5</v>
+        <v>39</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1.35</v>
+        <v>2.73</v>
       </c>
       <c r="K10" t="n">
-        <v>21.3</v>
+        <v>51.7</v>
       </c>
       <c r="L10" t="n">
-        <v>18.7</v>
+        <v>23.4</v>
       </c>
       <c r="M10" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.09</v>
+        <v>0.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>2371.3</v>
+        <v>3567.1</v>
       </c>
       <c r="R10" t="n">
-        <v>25.23</v>
+        <v>63.77</v>
       </c>
       <c r="S10" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="T10" t="n">
-        <v>3.23</v>
+        <v>8.27</v>
       </c>
       <c r="U10" t="n">
-        <v>3.03</v>
+        <v>0.78</v>
       </c>
       <c r="V10" t="n">
-        <v>35.3</v>
+        <v>-33.5</v>
       </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1898</v>
+        <v>0.2211</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1263,18 +1256,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="K11" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>20.2</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1283,1001 +1270,136 @@
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.12</v>
+        <v>-11.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>2625</v>
+        <v>546.8</v>
       </c>
       <c r="R11" t="n">
-        <v>57.11</v>
+        <v>18.01</v>
       </c>
       <c r="S11" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="T11" t="n">
-        <v>31.86</v>
+        <v>7.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>65</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.1978</v>
-      </c>
-      <c r="E12" t="n">
-        <v>58</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>⏸ 成長為負(-16%)</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rank 40 (納入線) 比重%</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.2947</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rank 60 (候補尾) 比重%</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2066</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rank 61 (剔除線) 比重%</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2056</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>我們 universe 在 TWSE 前 100 內</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>我們 universe 在 rank 41-60 卡位區</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>候選A (已體檢)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>候選B (blind spot)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2778.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>43.57</v>
-      </c>
-      <c r="S12" t="n">
-        <v>100</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V12" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>51</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="E13" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>57</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
-        <v>-5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2855.6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>15.52</v>
-      </c>
-      <c r="S13" t="n">
-        <v>68</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="V13" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>62</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.2051</v>
-      </c>
-      <c r="E14" t="n">
-        <v>56</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>82</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="K14" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2515.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>96</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>71</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>技嘉</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.1704</v>
-      </c>
-      <c r="E15" t="n">
-        <v>53</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>42</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2304.4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="S15" t="n">
-        <v>52</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>54</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="E16" t="n">
-        <v>50</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>64</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="K16" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3567.1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>63.77</v>
-      </c>
-      <c r="S16" t="n">
-        <v>82</v>
-      </c>
-      <c r="T16" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>78</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1438</v>
-      </c>
-      <c r="E17" t="n">
-        <v>48</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>51</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2227.6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>589.23</v>
-      </c>
-      <c r="S17" t="n">
-        <v>96</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>57</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.2211</v>
-      </c>
-      <c r="E18" t="n">
-        <v>43</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>26</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>-11.39</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>546.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="S18" t="n">
-        <v>91</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>175.8</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>73</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1632</v>
-      </c>
-      <c r="E19" t="n">
-        <v>43</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>34</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2306.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>19.77</v>
-      </c>
-      <c r="S19" t="n">
-        <v>99</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="V19" t="n">
-        <v>12</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>74</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>矽力*-KY</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.1605</v>
-      </c>
-      <c r="E20" t="n">
-        <v>35</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>27</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>626.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>86.45999999999999</v>
-      </c>
-      <c r="S20" t="n">
-        <v>66</v>
-      </c>
-      <c r="T20" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>79</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.1357</v>
-      </c>
-      <c r="E21" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>44</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>-5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1889</v>
-      </c>
-      <c r="R21" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="S21" t="n">
-        <v>62</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V21" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>64</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3034</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>聯詠</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.1996</v>
-      </c>
-      <c r="E22" t="n">
-        <v>26</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>22</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
-        <v>-10</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3310.3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="S22" t="n">
-        <v>97</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="V22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>90</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.1181</v>
-      </c>
-      <c r="E23" t="n">
-        <v>26</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>25</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1675</v>
-      </c>
-      <c r="R23" t="n">
-        <v>27.19</v>
-      </c>
-      <c r="S23" t="n">
-        <v>61</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>88</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.1226</v>
-      </c>
-      <c r="E24" t="n">
-        <v>16</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>36</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1715.8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>30.21</v>
-      </c>
-      <c r="S24" t="n">
-        <v>90</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="V24" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0050 剔除警報 (成分股逼近61名)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2291,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2323,20 +1445,20 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2011</v>
+        <v>0.2805</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2346,183 +1468,22 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1582</v>
+        <v>0.2762</v>
       </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>80</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1339</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>81</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>6531</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>愛普*</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.1331</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>82</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1329</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>83</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>華新科</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1316</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>86</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.1265</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>87</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1262</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>89</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1194</v>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>加入 PICKS 抓體檢</t>
         </is>
@@ -8261,7 +7222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8378,35 +7339,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>298.9</v>
+        <v>516</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8421,26 +7382,30 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="P2" t="n">
-        <v>0.92</v>
+        <v>1.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>51.64</v>
       </c>
       <c r="R2" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>4.32</v>
       </c>
       <c r="T2" t="n">
-        <v>2.24</v>
+        <v>1.37</v>
       </c>
       <c r="U2" t="n">
-        <v>58.3</v>
+        <v>16</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -8450,103 +7415,109 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>台特化</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>343.1</v>
+        <v>406.1</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K3" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>53.6</v>
+      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>🌱初拐點</t>
+        </is>
+      </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.19</v>
+        <v>58.47</v>
       </c>
       <c r="R3" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="S3" t="n">
-        <v>3.02</v>
+        <v>12.02</v>
       </c>
       <c r="T3" t="n">
-        <v>4.43</v>
+        <v>1.06</v>
       </c>
       <c r="U3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>241.2</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>313.4</v>
+        <v>298.9</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -8565,26 +7536,26 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>0.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>35.84</v>
+        <v>21</v>
       </c>
       <c r="R4" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="S4" t="n">
-        <v>3.82</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.05</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>37</v>
+        <v>58.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -8594,35 +7565,35 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>273</v>
+        <v>313.4</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8637,26 +7608,26 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.9</v>
+        <v>35.84</v>
       </c>
       <c r="R5" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="S5" t="n">
-        <v>8.57</v>
+        <v>3.82</v>
       </c>
       <c r="T5" t="n">
-        <v>2.79</v>
+        <v>1.05</v>
       </c>
       <c r="U5" t="n">
-        <v>15.4</v>
+        <v>37</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -8666,31 +7637,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>210.6</v>
+        <v>343.1</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -8699,18 +7670,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="K6" t="n">
-        <v>15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>13.5</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -8719,52 +7684,56 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.05</v>
+        <v>20.19</v>
       </c>
       <c r="R6" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="S6" t="n">
-        <v>3.37</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
+        <v>10.3</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>298.9</v>
+        <v>486.4</v>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -8773,12 +7742,18 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="K7" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.6</v>
+      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -8787,56 +7762,52 @@
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.79000000000001</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="S7" t="n">
-        <v>6.29</v>
+        <v>15.26</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>605.5</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>臺慶科</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>262</v>
+        <v>362.1</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -8845,18 +7816,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K8" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>60</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -8865,44 +7830,48 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.15</v>
+        <v>0.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>62.01</v>
+        <v>29.8</v>
       </c>
       <c r="R8" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="S8" t="n">
-        <v>32.45</v>
+        <v>3.65</v>
       </c>
       <c r="T8" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="U8" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
+        <v>37.8</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>286.8</v>
+        <v>353.1</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -8910,11 +7879,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8929,26 +7898,26 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>0.01</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>58.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S9" t="n">
-        <v>0.98</v>
+        <v>4.14</v>
       </c>
       <c r="T9" t="n">
-        <v>6.03</v>
+        <v>1.51</v>
       </c>
       <c r="U9" t="n">
-        <v>8.1</v>
+        <v>11.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8958,23 +7927,23 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>雙美</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>205.1</v>
+        <v>303.3</v>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -8982,141 +7951,143 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="K10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.13</v>
+        <v>0.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>28.33</v>
+        <v>64.42</v>
       </c>
       <c r="R10" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="S10" t="n">
-        <v>17.29</v>
+        <v>9.17</v>
       </c>
       <c r="T10" t="n">
-        <v>3.21</v>
+        <v>1.43</v>
       </c>
       <c r="U10" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
+        <v>-43.4</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>247.3</v>
+        <v>420.8</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>35.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-6%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
+        <v>-15</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>6.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.95</v>
+        <v>27.01</v>
       </c>
       <c r="R11" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="S11" t="n">
-        <v>4.37</v>
+        <v>5.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>3.46</v>
       </c>
       <c r="U11" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>353.1</v>
+        <v>299.1</v>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -9124,11 +8095,11 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9143,606 +8114,28 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>3.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>58.01</v>
+        <v>127.5</v>
       </c>
       <c r="R12" t="n">
         <v>100</v>
       </c>
       <c r="S12" t="n">
-        <v>4.14</v>
+        <v>1.13</v>
       </c>
       <c r="T12" t="n">
-        <v>1.51</v>
+        <v>0.65</v>
       </c>
       <c r="U12" t="n">
-        <v>11.8</v>
+        <v>6.1</v>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>64</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>6613</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>朋億*</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>286.3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>53</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>60</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>25.88</v>
-      </c>
-      <c r="R13" t="n">
-        <v>100</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U13" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>58</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>303.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>48</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>69</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>64.42</v>
-      </c>
-      <c r="R14" t="n">
-        <v>71</v>
-      </c>
-      <c r="S14" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-43.4</v>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>87</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6803</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>崑鼎</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>208.6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>46</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>36</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>🟢未來便宜</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K15" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="T15" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="V15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>59</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5371</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>299.1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>41</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>24</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>100</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="U16" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>62</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8064</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>東捷</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>288.3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>38</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>49</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>70.13</v>
-      </c>
-      <c r="R17" t="n">
-        <v>79</v>
-      </c>
-      <c r="S17" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>69</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>8027</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>鈦昇</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>260.7</v>
-      </c>
-      <c r="E18" t="n">
-        <v>30</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>20</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>251.19</v>
-      </c>
-      <c r="R18" t="n">
-        <v>93</v>
-      </c>
-      <c r="S18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>65</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>先進光</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>274.2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>23</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>65.81999999999999</v>
-      </c>
-      <c r="R19" t="n">
-        <v>52</v>
-      </c>
-      <c r="S19" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>81</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3587</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>閎康</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>217.4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>23</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>28</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
-        <v>-10</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="R20" t="n">
-        <v>97</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U20" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="V20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -9759,7 +8152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9791,20 +8184,20 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>信昌電陶</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>359.8</v>
+        <v>490.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -9814,20 +8207,20 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>德宏工業</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>354.7</v>
+        <v>460.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -9837,20 +8230,20 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>中國探針</t>
+          <t>漢磊</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>320</v>
+        <v>398.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -9860,20 +8253,20 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>元大期</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>320</v>
+        <v>396.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -9883,20 +8276,20 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>大國鋼</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>265.1</v>
+        <v>363.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -9906,20 +8299,20 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>254</v>
+        <v>359.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -9929,20 +8322,20 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>德宏工業</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>239.3</v>
+        <v>354.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -9952,20 +8345,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>德微</t>
+          <t>中國探針</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>236.4</v>
+        <v>320</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -9975,298 +8368,22 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>合一</t>
+          <t>元大期</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>233.5</v>
+        <v>320</v>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>75</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>8042</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>金山電子</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>230.6</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6664</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>群翊</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>229</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>77</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>6291</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>沛亨半導</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>228.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>78</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>5864</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>致和證</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>226.6</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>79</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>8096</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>224.8</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>80</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>7805</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>威聯通</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>224.6</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>82</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5009</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>榮剛材料</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>216.9</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>83</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6188</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>廣明光電</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>216.3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>84</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4971</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>IET-KY</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>215.9</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>85</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3693</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>營邦</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>213.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>89</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>6643</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>M31</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>205</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>90</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3526</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>凡甲科技</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="E22" t="inlineStr">
         <is>
           <t>加入 PICKS 抓體檢</t>
         </is>
@@ -12424,7 +10541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12478,7 +10595,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
+          <t>🔥轉上市即進0050(前40納入線)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12506,7 +10623,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
+          <t>🔥轉上市即進0050(前40納入線)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12534,7 +10651,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
+          <t>🔥轉上市即進0050(前40納入線)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12562,7 +10679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
+          <t>🔥轉上市即進0050(前40納入線)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -12590,7 +10707,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🔥轉上市即進0050(前50)</t>
+          <t>🔥轉上市即進0050(前40納入線)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -12618,178 +10735,10 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>⭐轉上市即進51-90</t>
+          <t>⭐轉上市即進候補(41-60)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>力旺電子</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2378.8</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>8069</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>元太</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2262.5</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>穩懋</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2213</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>鈊象電子</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2141.7</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2114</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>6147</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>頎邦科技</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1921</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>⭐轉上市即進51-90</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -12806,90 +10755,220 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>TWSE排名</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>值</t>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>比重%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>剔除警報</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>在我們PICKS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>rank 50 (邊緣) 比重%</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.2577</v>
-      </c>
+      <c r="A2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2077</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>🟡接近危險區(58-59)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rank 60 比重%</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>中鋼</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>0.2066</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>🟠逼近剔除線(60)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>rank 90 (候選下限) 比重%</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.1181</v>
+      <c r="A4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>瑞昱</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>🔴已跌出61名(剔除壓力)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>我們 universe 在 TWSE 前 100 內</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>68</v>
+      <c r="A5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>和泰車</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>🔴已跌出61名(剔除壓力)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>我們 universe 在 rank 51-90 內</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>27</v>
-      </c>
+      <c r="A6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>彰銀</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>🔴已跌出61名(剔除壓力)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>候選A (已體檢)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>23</v>
+      <c r="A7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2912</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>🔴已跌出61名(剔除壓力)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>候選B (blind spot)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>9</v>
-      </c>
+      <c r="A8" t="n">
+        <v>85</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5871</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>中租-KY</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>🔴已跌出61名(剔除壓力)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3762,1311 +3762,6 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>114</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>矽格</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>0.0757</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>115</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>5269</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>祥碩</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>0.07530000000000001</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>117</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>0.0738</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>118</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>禾伸堂</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>0.0731</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>119</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>0.0727</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>122</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>0.0693</v>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>125</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>志聖</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>0.0667</v>
-      </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>126</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>0.0658</v>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>132</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>崇越</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>0.0599</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>134</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>中興電</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>0.0576</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>135</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>群益證</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>金融🏦</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>138</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>南茂</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>0.0547</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>140</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>141</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>統一證</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>0.0523</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>金融🏦</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>142</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>3023</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>信邦</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>0.0521</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>145</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>6944</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>兆聯實業</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>0.0499</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>148</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>聯鈞</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0.0491</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>150</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>辛耘</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>0.0479</v>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>153</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>0.0467</v>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>158</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>3005</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>神基</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>0.0445</v>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>160</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2371</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>大同</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>0.0441</v>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>161</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>長榮航太</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>0.0429</v>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>164</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>6451</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>訊芯-KY</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>0.0426</v>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>172</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>4583</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>台灣精銳</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>0.0396</v>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>177</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>勝一</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>178</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>8926</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>180</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>國票金</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>0.0367</v>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>金融🏦</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>189</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>9917</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>中保科</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>0.0354</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>196</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>3715</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>定穎投控</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>0.0338</v>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>200</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2915</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>潤泰全</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>0.0334</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>531</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>3535</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>晶彩科</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>532</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>8341</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>日友</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>541</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>5292</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>華懋</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>0.0065</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>560</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>3504</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>揚明光</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>0.0061</v>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>572</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>584</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>6863</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>永道-KY</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>0.0056</v>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>587</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>3004</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>0.0055</v>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>589</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>7730</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>暉盛-創</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>590</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>9918</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>欣天然</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>613</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>一零四</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>655</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>4746</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>台耀</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>661</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2453</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>凌群</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>695</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>6776</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>展碁國際</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>701</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>6112</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>邁達特</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>710</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>5203</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>訊連</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>🟢便宜</t>
         </is>
       </c>
     </row>
@@ -5129,7 +3824,7 @@
         <v>41.992</v>
       </c>
       <c r="E2" t="n">
-        <v>650900</v>
+        <v>619784</v>
       </c>
     </row>
     <row r="3">
@@ -5150,7 +3845,7 @@
         <v>4.7532</v>
       </c>
       <c r="E3" t="n">
-        <v>73677</v>
+        <v>69128</v>
       </c>
     </row>
     <row r="4">
@@ -5171,7 +3866,7 @@
         <v>4.3669</v>
       </c>
       <c r="E4" t="n">
-        <v>67689</v>
+        <v>51431</v>
       </c>
     </row>
     <row r="5">
@@ -5192,7 +3887,7 @@
         <v>2.7827</v>
       </c>
       <c r="E5" t="n">
-        <v>43133</v>
+        <v>36124</v>
       </c>
     </row>
     <row r="6">
@@ -5213,7 +3908,7 @@
         <v>1.8741</v>
       </c>
       <c r="E6" t="n">
-        <v>29050</v>
+        <v>28656</v>
       </c>
     </row>
     <row r="7">
@@ -5234,7 +3929,7 @@
         <v>1.2615</v>
       </c>
       <c r="E7" t="n">
-        <v>19554</v>
+        <v>20209</v>
       </c>
     </row>
     <row r="8">
@@ -5255,7 +3950,7 @@
         <v>1.2498</v>
       </c>
       <c r="E8" t="n">
-        <v>19373</v>
+        <v>22450</v>
       </c>
     </row>
     <row r="9">
@@ -5276,7 +3971,7 @@
         <v>1.1429</v>
       </c>
       <c r="E9" t="n">
-        <v>17716</v>
+        <v>16207</v>
       </c>
     </row>
     <row r="10">
@@ -5297,7 +3992,7 @@
         <v>1.0594</v>
       </c>
       <c r="E10" t="n">
-        <v>16421</v>
+        <v>19050</v>
       </c>
     </row>
     <row r="11">
@@ -5311,14 +4006,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1.0519</v>
       </c>
       <c r="E11" t="n">
-        <v>16305</v>
+        <v>23304</v>
       </c>
     </row>
     <row r="12">
@@ -5339,7 +4034,7 @@
         <v>1.0219</v>
       </c>
       <c r="E12" t="n">
-        <v>15840</v>
+        <v>12451</v>
       </c>
     </row>
     <row r="13">
@@ -5360,7 +4055,7 @@
         <v>0.9375</v>
       </c>
       <c r="E13" t="n">
-        <v>14532</v>
+        <v>13355</v>
       </c>
     </row>
     <row r="14">
@@ -5381,7 +4076,7 @@
         <v>0.9004</v>
       </c>
       <c r="E14" t="n">
-        <v>13957</v>
+        <v>14157</v>
       </c>
     </row>
     <row r="15">
@@ -5402,7 +4097,7 @@
         <v>0.8643999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>13399</v>
+        <v>16356</v>
       </c>
     </row>
     <row r="16">
@@ -5423,7 +4118,7 @@
         <v>0.8186</v>
       </c>
       <c r="E16" t="n">
-        <v>12689</v>
+        <v>13892</v>
       </c>
     </row>
     <row r="17">
@@ -5444,7 +4139,7 @@
         <v>0.7393</v>
       </c>
       <c r="E17" t="n">
-        <v>11460</v>
+        <v>14780</v>
       </c>
     </row>
     <row r="18">
@@ -5465,7 +4160,7 @@
         <v>0.7368</v>
       </c>
       <c r="E18" t="n">
-        <v>11421</v>
+        <v>9292</v>
       </c>
     </row>
     <row r="19">
@@ -5486,7 +4181,7 @@
         <v>0.7308</v>
       </c>
       <c r="E19" t="n">
-        <v>11328</v>
+        <v>11171</v>
       </c>
     </row>
     <row r="20">
@@ -5507,7 +4202,7 @@
         <v>0.7186</v>
       </c>
       <c r="E20" t="n">
-        <v>11139</v>
+        <v>9833</v>
       </c>
     </row>
     <row r="21">
@@ -5528,7 +4223,7 @@
         <v>0.6958</v>
       </c>
       <c r="E21" t="n">
-        <v>10785</v>
+        <v>8446</v>
       </c>
     </row>
     <row r="22">
@@ -5549,7 +4244,7 @@
         <v>0.5463</v>
       </c>
       <c r="E22" t="n">
-        <v>8468</v>
+        <v>8892</v>
       </c>
     </row>
     <row r="23">
@@ -5570,7 +4265,7 @@
         <v>0.535</v>
       </c>
       <c r="E23" t="n">
-        <v>8293</v>
+        <v>12293</v>
       </c>
     </row>
     <row r="24">
@@ -5591,7 +4286,7 @@
         <v>0.4889</v>
       </c>
       <c r="E24" t="n">
-        <v>7578</v>
+        <v>9878</v>
       </c>
     </row>
     <row r="25">
@@ -5612,7 +4307,7 @@
         <v>0.4634</v>
       </c>
       <c r="E25" t="n">
-        <v>7183</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="26">
@@ -5633,7 +4328,7 @@
         <v>0.4303</v>
       </c>
       <c r="E26" t="n">
-        <v>6670</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="27">
@@ -5654,7 +4349,7 @@
         <v>0.408</v>
       </c>
       <c r="E27" t="n">
-        <v>6324</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="28">
@@ -5675,7 +4370,7 @@
         <v>0.3992</v>
       </c>
       <c r="E28" t="n">
-        <v>6188</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="29">
@@ -5696,7 +4391,7 @@
         <v>0.3887</v>
       </c>
       <c r="E29" t="n">
-        <v>6025</v>
+        <v>5556</v>
       </c>
     </row>
     <row r="30">
@@ -5717,7 +4412,7 @@
         <v>0.3791</v>
       </c>
       <c r="E30" t="n">
-        <v>5876</v>
+        <v>6445</v>
       </c>
     </row>
     <row r="31">
@@ -5738,7 +4433,7 @@
         <v>0.3768</v>
       </c>
       <c r="E31" t="n">
-        <v>5841</v>
+        <v>6752</v>
       </c>
     </row>
     <row r="32">
@@ -5759,7 +4454,7 @@
         <v>0.3736</v>
       </c>
       <c r="E32" t="n">
-        <v>5791</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="33">
@@ -5780,7 +4475,7 @@
         <v>0.3577</v>
       </c>
       <c r="E33" t="n">
-        <v>5545</v>
+        <v>4974</v>
       </c>
     </row>
     <row r="34">
@@ -5801,7 +4496,7 @@
         <v>0.3466</v>
       </c>
       <c r="E34" t="n">
-        <v>5372</v>
+        <v>5089</v>
       </c>
     </row>
     <row r="35">
@@ -5822,7 +4517,7 @@
         <v>0.3442</v>
       </c>
       <c r="E35" t="n">
-        <v>5335</v>
+        <v>5734</v>
       </c>
     </row>
     <row r="36">
@@ -5843,7 +4538,7 @@
         <v>0.3367</v>
       </c>
       <c r="E36" t="n">
-        <v>5219</v>
+        <v>5325</v>
       </c>
     </row>
     <row r="37">
@@ -5864,7 +4559,7 @@
         <v>0.3319</v>
       </c>
       <c r="E37" t="n">
-        <v>5145</v>
+        <v>6971</v>
       </c>
     </row>
     <row r="38">
@@ -5885,7 +4580,7 @@
         <v>0.3226</v>
       </c>
       <c r="E38" t="n">
-        <v>5000</v>
+        <v>6756</v>
       </c>
     </row>
     <row r="39">
@@ -5906,7 +4601,7 @@
         <v>0.3171</v>
       </c>
       <c r="E39" t="n">
-        <v>4915</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="40">
@@ -5927,7 +4622,7 @@
         <v>0.2989</v>
       </c>
       <c r="E40" t="n">
-        <v>4633</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="41">
@@ -5948,7 +4643,7 @@
         <v>0.2947</v>
       </c>
       <c r="E41" t="n">
-        <v>4568</v>
+        <v>4168</v>
       </c>
     </row>
     <row r="42">
@@ -5969,7 +4664,7 @@
         <v>0.2919</v>
       </c>
       <c r="E42" t="n">
-        <v>4525</v>
+        <v>5288</v>
       </c>
     </row>
     <row r="43">
@@ -5990,7 +4685,7 @@
         <v>0.2854</v>
       </c>
       <c r="E43" t="n">
-        <v>4424</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="44">
@@ -6011,7 +4706,7 @@
         <v>0.2805</v>
       </c>
       <c r="E44" t="n">
-        <v>4348</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="45">
@@ -6032,7 +4727,7 @@
         <v>0.2802</v>
       </c>
       <c r="E45" t="n">
-        <v>4343</v>
+        <v>5664</v>
       </c>
     </row>
     <row r="46">
@@ -6053,7 +4748,7 @@
         <v>0.2797</v>
       </c>
       <c r="E46" t="n">
-        <v>4336</v>
+        <v>3746</v>
       </c>
     </row>
     <row r="47">
@@ -6074,7 +4769,7 @@
         <v>0.2762</v>
       </c>
       <c r="E47" t="n">
-        <v>4281</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="48">
@@ -6095,7 +4790,7 @@
         <v>0.2714</v>
       </c>
       <c r="E48" t="n">
-        <v>4207</v>
+        <v>4724</v>
       </c>
     </row>
     <row r="49">
@@ -6116,7 +4811,7 @@
         <v>0.2641</v>
       </c>
       <c r="E49" t="n">
-        <v>4094</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="50">
@@ -6137,7 +4832,7 @@
         <v>0.2626</v>
       </c>
       <c r="E50" t="n">
-        <v>4070</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="51">
@@ -6158,7 +4853,7 @@
         <v>0.2577</v>
       </c>
       <c r="E51" t="n">
-        <v>3994</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="52">
@@ -6179,7 +4874,7 @@
         <v>0.251</v>
       </c>
       <c r="E52" t="n">
-        <v>3891</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="53">
@@ -6200,7 +4895,7 @@
         <v>0.2464</v>
       </c>
       <c r="E53" t="n">
-        <v>3819</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="54">
@@ -6221,7 +4916,7 @@
         <v>0.2429</v>
       </c>
       <c r="E54" t="n">
-        <v>3765</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="55">
@@ -6242,7 +4937,7 @@
         <v>0.2408</v>
       </c>
       <c r="E55" t="n">
-        <v>3733</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="56">
@@ -6263,7 +4958,7 @@
         <v>0.2331</v>
       </c>
       <c r="E56" t="n">
-        <v>3613</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="57">
@@ -6284,7 +4979,7 @@
         <v>0.2285</v>
       </c>
       <c r="E57" t="n">
-        <v>3542</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="58">
@@ -6305,7 +5000,7 @@
         <v>0.2211</v>
       </c>
       <c r="E58" t="n">
-        <v>3427</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="59">
@@ -6326,7 +5021,7 @@
         <v>0.2147</v>
       </c>
       <c r="E59" t="n">
-        <v>3328</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="60">
@@ -6347,7 +5042,7 @@
         <v>0.2077</v>
       </c>
       <c r="E60" t="n">
-        <v>3219</v>
+        <v>3692</v>
       </c>
     </row>
     <row r="61">
@@ -6368,7 +5063,7 @@
         <v>0.2066</v>
       </c>
       <c r="E61" t="n">
-        <v>3202</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="62">
@@ -6389,7 +5084,7 @@
         <v>0.2056</v>
       </c>
       <c r="E62" t="n">
-        <v>3187</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="63">
@@ -6410,7 +5105,7 @@
         <v>0.2051</v>
       </c>
       <c r="E63" t="n">
-        <v>3179</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="64">
@@ -6431,7 +5126,7 @@
         <v>0.2011</v>
       </c>
       <c r="E64" t="n">
-        <v>3117</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="65">
@@ -6452,7 +5147,7 @@
         <v>0.1996</v>
       </c>
       <c r="E65" t="n">
-        <v>3094</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="66">
@@ -6473,7 +5168,7 @@
         <v>0.1978</v>
       </c>
       <c r="E66" t="n">
-        <v>3066</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="67">
@@ -6494,7 +5189,7 @@
         <v>0.1925</v>
       </c>
       <c r="E67" t="n">
-        <v>2984</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="68">
@@ -6515,7 +5210,7 @@
         <v>0.1898</v>
       </c>
       <c r="E68" t="n">
-        <v>2942</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="69">
@@ -6536,7 +5231,7 @@
         <v>0.1883</v>
       </c>
       <c r="E69" t="n">
-        <v>2919</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="70">
@@ -6557,7 +5252,7 @@
         <v>0.185</v>
       </c>
       <c r="E70" t="n">
-        <v>2868</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="71">
@@ -6578,7 +5273,7 @@
         <v>0.1732</v>
       </c>
       <c r="E71" t="n">
-        <v>2685</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="72">
@@ -6599,7 +5294,7 @@
         <v>0.1704</v>
       </c>
       <c r="E72" t="n">
-        <v>2641</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="73">
@@ -6620,7 +5315,7 @@
         <v>0.1638</v>
       </c>
       <c r="E73" t="n">
-        <v>2539</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="74">
@@ -6641,7 +5336,7 @@
         <v>0.1632</v>
       </c>
       <c r="E74" t="n">
-        <v>2530</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="75">
@@ -6655,14 +5350,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>矽力-KY</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>0.1605</v>
       </c>
       <c r="E75" t="n">
-        <v>2488</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="76">
@@ -6683,7 +5378,7 @@
         <v>0.1582</v>
       </c>
       <c r="E76" t="n">
-        <v>2452</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="77">
@@ -6704,7 +5399,7 @@
         <v>0.153</v>
       </c>
       <c r="E77" t="n">
-        <v>2372</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="78">
@@ -6725,7 +5420,7 @@
         <v>0.1514</v>
       </c>
       <c r="E78" t="n">
-        <v>2347</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="79">
@@ -6746,7 +5441,7 @@
         <v>0.1438</v>
       </c>
       <c r="E79" t="n">
-        <v>2229</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="80">
@@ -6767,7 +5462,7 @@
         <v>0.1357</v>
       </c>
       <c r="E80" t="n">
-        <v>2103</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="81">
@@ -6788,7 +5483,7 @@
         <v>0.1339</v>
       </c>
       <c r="E81" t="n">
-        <v>2076</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="82">
@@ -6802,14 +5497,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>愛普</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>0.1331</v>
       </c>
       <c r="E82" t="n">
-        <v>2063</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="83">
@@ -6830,7 +5525,7 @@
         <v>0.1329</v>
       </c>
       <c r="E83" t="n">
-        <v>2060</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="84">
@@ -6851,7 +5546,7 @@
         <v>0.1316</v>
       </c>
       <c r="E84" t="n">
-        <v>2040</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="85">
@@ -6872,7 +5567,7 @@
         <v>0.127</v>
       </c>
       <c r="E85" t="n">
-        <v>1969</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="86">
@@ -6893,7 +5588,7 @@
         <v>0.1265</v>
       </c>
       <c r="E86" t="n">
-        <v>1961</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="87">
@@ -6914,7 +5609,7 @@
         <v>0.1265</v>
       </c>
       <c r="E87" t="n">
-        <v>1961</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="88">
@@ -6935,7 +5630,7 @@
         <v>0.1262</v>
       </c>
       <c r="E88" t="n">
-        <v>1956</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="89">
@@ -6956,7 +5651,7 @@
         <v>0.1226</v>
       </c>
       <c r="E89" t="n">
-        <v>1900</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="90">
@@ -6977,7 +5672,7 @@
         <v>0.1194</v>
       </c>
       <c r="E90" t="n">
-        <v>1851</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="91">
@@ -6998,7 +5693,7 @@
         <v>0.1181</v>
       </c>
       <c r="E91" t="n">
-        <v>1831</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="92">
@@ -7019,7 +5714,7 @@
         <v>0.1181</v>
       </c>
       <c r="E92" t="n">
-        <v>1831</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="93">
@@ -7040,7 +5735,7 @@
         <v>0.1176</v>
       </c>
       <c r="E93" t="n">
-        <v>1823</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="94">
@@ -7061,7 +5756,7 @@
         <v>0.1151</v>
       </c>
       <c r="E94" t="n">
-        <v>1784</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="95">
@@ -7082,7 +5777,7 @@
         <v>0.1112</v>
       </c>
       <c r="E95" t="n">
-        <v>1724</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="96">
@@ -7103,7 +5798,7 @@
         <v>0.1086</v>
       </c>
       <c r="E96" t="n">
-        <v>1683</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="97">
@@ -7117,14 +5812,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>康霈</t>
         </is>
       </c>
       <c r="D97" t="n">
         <v>0.1076</v>
       </c>
       <c r="E97" t="n">
-        <v>1668</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="98">
@@ -7145,7 +5840,7 @@
         <v>0.1061</v>
       </c>
       <c r="E98" t="n">
-        <v>1645</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="99">
@@ -7166,7 +5861,7 @@
         <v>0.1001</v>
       </c>
       <c r="E99" t="n">
-        <v>1552</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="100">
@@ -7187,7 +5882,7 @@
         <v>0.099</v>
       </c>
       <c r="E100" t="n">
-        <v>1535</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="101">
@@ -7208,7 +5903,7 @@
         <v>0.0985</v>
       </c>
       <c r="E101" t="n">
-        <v>1527</v>
+        <v>1585</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -26,13 +26,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +46,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +54,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,117 +438,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>市值(億)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -1311,12 +1323,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>值</t>
         </is>
@@ -1417,27 +1429,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -1504,37 +1516,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>是否0050</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -3780,27 +3792,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -5921,112 +5933,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>OTC市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -6851,27 +6863,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -7099,27 +7111,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>收盤</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -9240,32 +9252,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>轉上市定位</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>在我們PICKS</t>
         </is>
@@ -9454,32 +9466,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>剔除警報</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>在我們PICKS</t>
         </is>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -15,8 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富櫃50候選B_blind" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OTC前100" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OTC轉上市觀察" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0050剔除警報" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="門檻說明" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="門檻說明" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,31 +918,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2285</v>
+        <v>0.2802</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -952,75 +951,73 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="K7" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5.5</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3895.6</v>
+        <v>5272.9</v>
       </c>
       <c r="R7" t="n">
-        <v>27.34</v>
+        <v>600</v>
       </c>
       <c r="S7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T7" t="n">
-        <v>4.06</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>3.53</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
+        <v>10.3</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2802</v>
+        <v>0.251</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1036,32 +1033,32 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>21.3</v>
+        <v>-0.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5272.9</v>
+        <v>2855.6</v>
       </c>
       <c r="R8" t="n">
-        <v>600</v>
+        <v>15.52</v>
       </c>
       <c r="S8" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="T8" t="n">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>3.47</v>
       </c>
       <c r="V8" t="n">
-        <v>10.3</v>
+        <v>152.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1071,31 +1068,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.251</v>
+        <v>0.2211</v>
       </c>
       <c r="E9" t="n">
-        <v>46.5</v>
+        <v>33</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1111,295 +1108,37 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>-0.2</v>
+        <v>-11.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>2855.6</v>
+        <v>546.8</v>
       </c>
       <c r="R9" t="n">
-        <v>15.52</v>
+        <v>18.01</v>
       </c>
       <c r="S9" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="T9" t="n">
-        <v>2.53</v>
+        <v>7.25</v>
       </c>
       <c r="U9" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>152.7</v>
+        <v>175.8</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>54</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="E10" t="n">
-        <v>39</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>64</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="K10" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3567.1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>63.77</v>
-      </c>
-      <c r="S10" t="n">
-        <v>82</v>
-      </c>
-      <c r="T10" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.2211</v>
-      </c>
-      <c r="E11" t="n">
-        <v>33</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>26</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>-11.39</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>546.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="S11" t="n">
-        <v>91</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>175.8</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>rank 40 (納入線) 比重%</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.2947</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rank 60 (候補尾) 比重%</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.2066</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>rank 61 (剔除線) 比重%</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.2056</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>我們 universe 在 TWSE 前 100 內</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>我們 universe 在 rank 41-60 卡位區</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>候選A (已體檢)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>候選B (blind spot)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>0050 剔除警報 (成分股逼近61名)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1445,20 +1184,20 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2805</v>
+        <v>0.2077</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1468,20 +1207,20 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2762</v>
+        <v>0.2066</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1656,7 +1395,11 @@
       <c r="D5" t="n">
         <v>1.2615</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>A</t>
@@ -1685,7 +1428,11 @@
       <c r="D6" t="n">
         <v>1.1429</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>D</t>
@@ -1747,7 +1494,11 @@
       <c r="D8" t="n">
         <v>1.0519</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>C</t>
@@ -1776,7 +1527,11 @@
       <c r="D9" t="n">
         <v>0.9375</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>A</t>
@@ -1871,7 +1626,11 @@
       <c r="D12" t="n">
         <v>0.7393</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>C</t>
@@ -1900,7 +1659,11 @@
       <c r="D13" t="n">
         <v>0.7368</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>A</t>
@@ -1962,7 +1725,11 @@
       <c r="D15" t="n">
         <v>0.7186</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>A</t>
@@ -2024,7 +1791,11 @@
       <c r="D17" t="n">
         <v>0.4889</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>C</t>
@@ -2053,7 +1824,11 @@
       <c r="D18" t="n">
         <v>0.4634</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>A</t>
@@ -2181,7 +1956,11 @@
       <c r="D22" t="n">
         <v>0.3887</v>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>D</t>
@@ -2309,7 +2088,11 @@
       <c r="D26" t="n">
         <v>0.3577</v>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>A</t>
@@ -2404,7 +2187,11 @@
       <c r="D29" t="n">
         <v>0.3319</v>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>A</t>
@@ -2842,7 +2629,11 @@
       <c r="D43" t="n">
         <v>0.2408</v>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>C</t>
@@ -2900,7 +2691,11 @@
       <c r="D45" t="n">
         <v>0.2285</v>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>B</t>
@@ -2987,11 +2782,7 @@
       <c r="D48" t="n">
         <v>0.2056</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>C</t>
@@ -3194,11 +2985,7 @@
       <c r="D55" t="n">
         <v>0.185</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>B</t>
@@ -3343,11 +3130,7 @@
       <c r="D60" t="n">
         <v>0.153</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>C</t>
@@ -9450,220 +9233,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TWSE排名</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>比重%</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>剔除警報</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>在我們PICKS</t>
+          <t>值</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.2077</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>🟡接近危險區(58-59)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rank 40 (納入線) 比重%</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.2947</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>60</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rank 60 (候補尾) 比重%</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>0.2066</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>🟠逼近剔除線(60)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>瑞昱</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rank 61 (剔除線) 比重%</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.2056</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>🔴已跌出61名(剔除壓力)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>69</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2207</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>和泰車</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>🔴已跌出61名(剔除壓力)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>我們 universe 在 TWSE 前 100 內</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>72</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1638</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>🔴已跌出61名(剔除壓力)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>我們 universe 在 rank 41-60 卡位區</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>76</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>🔴已跌出61名(剔除壓力)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>候選A (已體檢)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>85</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>5871</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>中租-KY</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.1265</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>🔴已跌出61名(剔除壓力)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>候選B (blind spot)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0050 剔除警報 (成分股逼近61名)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -25,13 +25,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,117 +437,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>市值(億)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -1156,27 +1168,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -1243,37 +1255,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>是否0050</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -3563,27 +3575,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -5704,112 +5716,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>OTC市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -6634,27 +6646,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -6882,27 +6894,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>收盤</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -9023,32 +9035,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>轉上市定位</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>在我們PICKS</t>
         </is>
@@ -9237,12 +9249,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>值</t>
         </is>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,121 +421,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>市值(億)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -1080,23 +1068,23 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2211</v>
+        <v>0.2077</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1104,11 +1092,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1123,31 +1111,181 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2851.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="S9" t="n">
+        <v>66</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>60</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中鋼</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="E10" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>-7.94</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3091.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>178.64</v>
+      </c>
+      <c r="S10" t="n">
+        <v>92</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>57</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="E11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>-11.39</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q11" t="n">
         <v>546.8</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R11" t="n">
         <v>18.01</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S11" t="n">
         <v>91</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>7.25</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V11" t="n">
         <v>175.8</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -1164,79 +1302,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>建議</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.2077</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>60</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.2066</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
         </is>
       </c>
     </row>
@@ -1251,41 +1343,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>是否0050</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -1788,20 +1880,20 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.4889</v>
+        <v>0.535</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1810,7 +1902,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1821,20 +1913,20 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4634</v>
+        <v>0.4889</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1843,7 +1935,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1854,20 +1946,20 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.4303</v>
+        <v>0.4634</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1876,7 +1968,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1887,20 +1979,20 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.408</v>
+        <v>0.4303</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1909,7 +2001,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1920,20 +2012,20 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.3992</v>
+        <v>0.408</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1953,20 +2045,20 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.3887</v>
+        <v>0.3992</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1975,7 +2067,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1986,20 +2078,20 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.3791</v>
+        <v>0.3887</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2008,7 +2100,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2019,20 +2111,20 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.3768</v>
+        <v>0.3791</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2041,7 +2133,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2052,20 +2144,20 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.3736</v>
+        <v>0.3768</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2074,7 +2166,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2085,20 +2177,20 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.3577</v>
+        <v>0.3736</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2107,7 +2199,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2118,20 +2210,20 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.3442</v>
+        <v>0.3577</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2140,31 +2232,31 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.3367</v>
+        <v>0.3442</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2173,31 +2265,31 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.3319</v>
+        <v>0.3367</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2206,31 +2298,31 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.3226</v>
+        <v>0.3319</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2239,7 +2331,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2250,20 +2342,20 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.2989</v>
+        <v>0.3226</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2272,7 +2364,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2283,20 +2375,20 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.2947</v>
+        <v>0.2989</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2305,7 +2397,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2316,20 +2408,20 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2919</v>
+        <v>0.2947</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2338,7 +2430,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2349,20 +2441,20 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.2854</v>
+        <v>0.2919</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2371,60 +2463,64 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.2802</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>0.2854</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.2797</v>
+        <v>0.2805</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2433,36 +2529,36 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.2641</v>
+        <v>0.2802</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2473,20 +2569,20 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2626</v>
+        <v>0.2797</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2495,7 +2591,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2506,25 +2602,25 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.2577</v>
+        <v>0.2641</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2535,25 +2631,29 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
+        <v>0.2626</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2564,82 +2664,78 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2464</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2577</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.2429</v>
+        <v>0.251</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.2408</v>
+        <v>0.2464</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2648,60 +2744,60 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2331</v>
+        <v>0.2429</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2285</v>
+        <v>0.2408</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2710,36 +2806,36 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.2211</v>
+        <v>0.2331</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2750,25 +2846,29 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.2147</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
+        <v>0.2285</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2779,25 +2879,25 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.2056</v>
+        <v>0.2211</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2808,20 +2908,20 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.2051</v>
+        <v>0.2147</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
@@ -2837,20 +2937,20 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.1996</v>
+        <v>0.2077</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
@@ -2860,26 +2960,26 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.1978</v>
+        <v>0.2066</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
@@ -2889,55 +2989,55 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.1925</v>
+        <v>0.2056</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.1898</v>
+        <v>0.2051</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
@@ -2953,83 +3053,83 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.1883</v>
+        <v>0.2011</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.185</v>
+        <v>0.1996</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.1732</v>
+        <v>0.1978</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3040,112 +3140,112 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.1704</v>
+        <v>0.1925</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.1632</v>
+        <v>0.1898</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.1605</v>
+        <v>0.1883</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.153</v>
+        <v>0.185</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3156,25 +3256,25 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.1514</v>
+        <v>0.1732</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3185,49 +3285,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.1438</v>
+        <v>0.1704</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1357</v>
+        <v>0.1632</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
@@ -3243,112 +3343,112 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.127</v>
+        <v>0.1605</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.1226</v>
+        <v>0.153</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.1181</v>
+        <v>0.1514</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.1176</v>
+        <v>0.1438</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3359,49 +3459,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.1001</v>
+        <v>0.1357</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.099</v>
+        <v>0.127</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
@@ -3417,20 +3517,20 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0946</v>
+        <v>0.1262</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
@@ -3440,26 +3540,26 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0851</v>
+        <v>0.1226</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -3475,49 +3575,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.0784</v>
+        <v>0.1181</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.0774</v>
+        <v>0.1176</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
@@ -3533,28 +3633,260 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.0764</v>
+        <v>0.1001</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>🟡合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>99</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>101</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>上銀</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>102</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>遠東新</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.0944</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>104</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>105</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>109</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>士電</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>110</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>111</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>台中銀</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>金融🏦</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
         </is>
@@ -3575,27 +3907,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>比重%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -5716,112 +6048,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OTC市值億</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -6646,27 +6978,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -6894,27 +7226,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>收盤</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -9035,32 +9367,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>轉上市定位</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>在我們PICKS</t>
         </is>
@@ -9249,12 +9581,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>值</t>
         </is>
@@ -9297,7 +9629,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -9307,7 +9639,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -9317,7 +9649,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -9327,7 +9659,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -25,13 +25,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,117 +437,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>市值(億)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -1306,27 +1318,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -1343,41 +1355,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TWSE排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>大盤比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>是否0050</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
@@ -1451,20 +1463,20 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.8741</v>
+        <v>2.7827</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1484,20 +1496,20 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.2615</v>
+        <v>1.8741</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1506,31 +1518,31 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.1429</v>
+        <v>1.2615</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1539,31 +1551,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.0594</v>
+        <v>1.2498</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1572,7 +1584,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1583,20 +1595,20 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.0519</v>
+        <v>1.1429</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1605,7 +1617,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1616,20 +1628,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9375</v>
+        <v>1.0594</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1638,7 +1650,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1649,20 +1661,20 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8643999999999999</v>
+        <v>1.0519</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1671,7 +1683,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1682,20 +1694,20 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8186</v>
+        <v>0.9375</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1704,7 +1716,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1715,20 +1727,20 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7393</v>
+        <v>0.9004</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1737,7 +1749,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1748,20 +1760,20 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7368</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1770,7 +1782,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1781,20 +1793,20 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7308</v>
+        <v>0.8186</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1803,7 +1815,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1814,20 +1826,20 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7186</v>
+        <v>0.7393</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1836,31 +1848,31 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5463</v>
+        <v>0.7368</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1869,7 +1881,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1880,20 +1892,20 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.535</v>
+        <v>0.7308</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1902,7 +1914,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1913,20 +1925,20 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4889</v>
+        <v>0.7186</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1935,31 +1947,31 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.4634</v>
+        <v>0.5463</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1968,7 +1980,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1979,20 +1991,20 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.4303</v>
+        <v>0.535</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2001,7 +2013,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2012,20 +2024,20 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.408</v>
+        <v>0.4889</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2034,7 +2046,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2045,20 +2057,20 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.3992</v>
+        <v>0.4634</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2067,7 +2079,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2078,20 +2090,20 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.3887</v>
+        <v>0.4303</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2100,7 +2112,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2111,20 +2123,20 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.3791</v>
+        <v>0.408</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2133,7 +2145,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2144,20 +2156,20 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.3768</v>
+        <v>0.3992</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2166,7 +2178,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2177,20 +2189,20 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.3736</v>
+        <v>0.3887</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2199,7 +2211,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2210,20 +2222,20 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.3577</v>
+        <v>0.3791</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2232,7 +2244,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2243,20 +2255,20 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.3442</v>
+        <v>0.3768</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2265,31 +2277,31 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.3367</v>
+        <v>0.3736</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2303,26 +2315,26 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.3319</v>
+        <v>0.3577</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2342,20 +2354,20 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.3226</v>
+        <v>0.3442</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2364,31 +2376,31 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.2989</v>
+        <v>0.3367</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2397,31 +2409,31 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2947</v>
+        <v>0.3319</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2430,7 +2442,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2441,20 +2453,20 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.2919</v>
+        <v>0.3226</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2463,7 +2475,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2474,20 +2486,20 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.2854</v>
+        <v>0.2989</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2496,31 +2508,31 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.2805</v>
+        <v>0.2947</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2529,36 +2541,40 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.2802</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
+        <v>0.2919</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2569,20 +2585,20 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2797</v>
+        <v>0.2854</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2596,64 +2612,64 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.2641</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
+        <v>0.2805</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.2626</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2802</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2664,25 +2680,29 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2577</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
+        <v>0.2797</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2693,20 +2713,20 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.251</v>
+        <v>0.2641</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
@@ -2722,20 +2742,20 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.2464</v>
+        <v>0.2626</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2749,61 +2769,57 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2429</v>
+        <v>0.2577</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.251</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>C</t>
@@ -2811,61 +2827,61 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.2331</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>0.2464</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.2285</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2429</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>B</t>
@@ -2873,55 +2889,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.2211</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
+        <v>0.2408</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.2147</v>
+        <v>0.2331</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
@@ -2937,49 +2957,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.2077</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+        <v>0.2285</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.2066</v>
+        <v>0.2211</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
@@ -2989,31 +3013,31 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.2056</v>
+        <v>0.2147</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3024,49 +3048,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.2051</v>
+        <v>0.2077</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.2011</v>
+        <v>0.2066</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
@@ -3076,60 +3100,60 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.1996</v>
+        <v>0.2056</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.1978</v>
+        <v>0.2051</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3140,83 +3164,83 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.1925</v>
+        <v>0.2011</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.1898</v>
+        <v>0.1996</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.1883</v>
+        <v>0.1978</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3227,20 +3251,20 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.185</v>
+        <v>0.1925</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
@@ -3250,31 +3274,31 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.1732</v>
+        <v>0.1898</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3285,112 +3309,112 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.1704</v>
+        <v>0.1883</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1632</v>
+        <v>0.185</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.1605</v>
+        <v>0.1732</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.153</v>
+        <v>0.1704</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3401,107 +3425,107 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.1514</v>
+        <v>0.1632</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.1438</v>
+        <v>0.1605</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.1357</v>
+        <v>0.153</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.127</v>
+        <v>0.1514</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
@@ -3517,49 +3541,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.1262</v>
+        <v>0.1438</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.1226</v>
+        <v>0.1357</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -3569,118 +3593,118 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.1181</v>
+        <v>0.127</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.1176</v>
+        <v>0.1262</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.1001</v>
+        <v>0.1226</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.099</v>
+        <v>0.1194</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3691,20 +3715,20 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.0946</v>
+        <v>0.1181</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
@@ -3714,55 +3738,55 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0944</v>
+        <v>0.1176</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0851</v>
+        <v>0.1112</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
@@ -3778,54 +3802,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.0829</v>
+        <v>0.1001</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.0784</v>
+        <v>0.099</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3836,25 +3860,25 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0774</v>
+        <v>0.0985</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3865,28 +3889,202 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0764</v>
+        <v>0.0946</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>102</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>遠東新</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.0944</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>104</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>105</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>109</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>士電</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>110</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>111</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>台中銀</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>金融🏦</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
         </is>
@@ -3907,27 +4105,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>比重%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -6048,112 +6246,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>OTC市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>納入潛力分</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>改善訊號數</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>分級</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
@@ -6978,27 +7176,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>建議</t>
         </is>
@@ -7226,27 +7424,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>收盤</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
@@ -9367,32 +9565,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OTC排名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>市值億</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>轉上市定位</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>在我們PICKS</t>
         </is>
@@ -9581,12 +9779,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>值</t>
         </is>
@@ -9629,7 +9827,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -1355,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1430,20 +1430,20 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.3669</v>
+        <v>4.7532</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1463,20 +1463,20 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.7827</v>
+        <v>4.3669</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1496,20 +1496,20 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.8741</v>
+        <v>2.7827</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1529,20 +1529,20 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.2615</v>
+        <v>1.8741</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1551,31 +1551,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.2498</v>
+        <v>1.2615</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1584,31 +1584,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.1429</v>
+        <v>1.2498</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1628,20 +1628,20 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.0594</v>
+        <v>1.1429</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1661,20 +1661,20 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.0519</v>
+        <v>1.0594</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1694,20 +1694,20 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9375</v>
+        <v>1.0519</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1727,20 +1727,20 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9004</v>
+        <v>0.9375</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1760,20 +1760,20 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.9004</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1793,20 +1793,20 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.8186</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1826,20 +1826,20 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7393</v>
+        <v>0.8186</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1859,20 +1859,20 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7368</v>
+        <v>0.7393</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1892,20 +1892,20 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7308</v>
+        <v>0.7368</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1925,20 +1925,20 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.7186</v>
+        <v>0.7308</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1947,31 +1947,31 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5463</v>
+        <v>0.7186</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1980,31 +1980,31 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.535</v>
+        <v>0.5463</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2024,20 +2024,20 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.4889</v>
+        <v>0.535</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2057,20 +2057,20 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.4634</v>
+        <v>0.4889</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2090,20 +2090,20 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.4303</v>
+        <v>0.4634</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2123,20 +2123,20 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.408</v>
+        <v>0.4303</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2156,20 +2156,20 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.3992</v>
+        <v>0.408</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2189,20 +2189,20 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.3887</v>
+        <v>0.3992</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2222,20 +2222,20 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.3791</v>
+        <v>0.3887</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2255,20 +2255,20 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.3768</v>
+        <v>0.3791</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2288,20 +2288,20 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.3736</v>
+        <v>0.3768</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2321,20 +2321,20 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.3577</v>
+        <v>0.3736</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2354,20 +2354,20 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.3442</v>
+        <v>0.3577</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2376,31 +2376,31 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.3367</v>
+        <v>0.3442</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2409,31 +2409,31 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3319</v>
+        <v>0.3367</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2442,31 +2442,31 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.3226</v>
+        <v>0.3319</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2486,20 +2486,20 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.2989</v>
+        <v>0.3226</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2519,20 +2519,20 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.2947</v>
+        <v>0.3171</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2541,31 +2541,31 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.2919</v>
+        <v>0.2989</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2585,20 +2585,20 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2854</v>
+        <v>0.2947</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2607,31 +2607,31 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.2805</v>
+        <v>0.2919</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2640,60 +2640,64 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.2802</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
+        <v>0.2854</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2797</v>
+        <v>0.2805</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2702,36 +2706,36 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.2641</v>
+        <v>0.2802</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2742,20 +2746,20 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.2626</v>
+        <v>0.2797</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2764,7 +2768,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2775,25 +2779,29 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2577</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>0.2762</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2804,25 +2812,29 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+        <v>0.2714</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2833,120 +2845,116 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.2464</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2641</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.2429</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
+        <v>0.2626</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2577</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.2331</v>
+        <v>0.251</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2957,20 +2965,20 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.2285</v>
+        <v>0.2464</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2979,152 +2987,160 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.2211</v>
+        <v>0.2429</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.2147</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
+        <v>0.2408</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.2077</v>
+        <v>0.2331</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.2066</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>0.2285</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.2056</v>
+        <v>0.2211</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3135,20 +3151,20 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.2051</v>
+        <v>0.2147</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
@@ -3164,20 +3180,20 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.2011</v>
+        <v>0.2077</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
@@ -3187,26 +3203,26 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.1996</v>
+        <v>0.2066</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
@@ -3216,31 +3232,31 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.1978</v>
+        <v>0.2056</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3251,136 +3267,136 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.1925</v>
+        <v>0.2051</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.1898</v>
+        <v>0.2011</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.1883</v>
+        <v>0.1996</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.185</v>
+        <v>0.1978</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.1732</v>
+        <v>0.1925</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -3390,200 +3406,200 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.1704</v>
+        <v>0.1898</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.1632</v>
+        <v>0.1883</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.1605</v>
+        <v>0.185</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.153</v>
+        <v>0.1732</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.1514</v>
+        <v>0.1704</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>彰銀</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.1438</v>
+        <v>0.1638</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.1357</v>
+        <v>0.1632</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -3599,49 +3615,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.127</v>
+        <v>0.1605</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.1262</v>
+        <v>0.1582</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
@@ -3657,54 +3673,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.1226</v>
+        <v>0.153</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.1194</v>
+        <v>0.1514</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3715,136 +3731,136 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.1181</v>
+        <v>0.1438</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.1176</v>
+        <v>0.1357</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.1112</v>
+        <v>0.1339</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.1001</v>
+        <v>0.1316</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.099</v>
+        <v>0.127</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
@@ -3860,20 +3876,20 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.0985</v>
+        <v>0.1265</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -3883,26 +3899,26 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.0946</v>
+        <v>0.1262</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
@@ -3912,55 +3928,55 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.0944</v>
+        <v>0.1226</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0851</v>
+        <v>0.1194</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
@@ -3976,20 +3992,20 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.0829</v>
+        <v>0.1181</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
@@ -3999,31 +4015,31 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.0784</v>
+        <v>0.1176</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4034,25 +4050,25 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.0774</v>
+        <v>0.1112</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4063,20 +4079,20 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>臺企銀</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.0764</v>
+        <v>0.1086</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
@@ -4085,6 +4101,354 @@
         </is>
       </c>
       <c r="G88" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>98</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2451</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>創見</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>🟡合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>99</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>100</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>101</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>上銀</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>102</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>遠東新</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.0944</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>104</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>105</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>107</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>華航</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.0799</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>108</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>可成</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>109</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>士電</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>110</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>111</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>台中銀</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>金融🏦</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
         </is>
@@ -9827,7 +10191,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -9837,7 +10201,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -1355,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2387,20 +2387,20 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.3442</v>
+        <v>0.3466</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2409,31 +2409,31 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3367</v>
+        <v>0.3442</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2442,31 +2442,31 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.3319</v>
+        <v>0.3367</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2475,31 +2475,31 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.3226</v>
+        <v>0.3319</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2519,20 +2519,20 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.3171</v>
+        <v>0.3226</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2541,31 +2541,31 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.2989</v>
+        <v>0.3171</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2574,31 +2574,31 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2947</v>
+        <v>0.2989</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2618,20 +2618,20 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.2919</v>
+        <v>0.2947</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2651,20 +2651,20 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.2854</v>
+        <v>0.2919</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2673,31 +2673,31 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2805</v>
+        <v>0.2854</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2717,22 +2717,26 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.2802</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
+        <v>0.2805</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>D</t>
@@ -2740,35 +2744,31 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.2797</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2802</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2779,20 +2779,20 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2762</v>
+        <v>0.2797</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2812,20 +2812,20 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2714</v>
+        <v>0.2762</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2845,25 +2845,29 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.2641</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>0.2714</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2874,29 +2878,25 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.2626</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2641</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2907,25 +2907,29 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.2577</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
+        <v>0.2626</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2936,25 +2940,25 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.251</v>
+        <v>0.2577</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2965,91 +2969,87 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.2464</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.251</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.2429</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
+        <v>0.2464</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2429</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3060,58 +3060,58 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.2331</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
+        <v>0.2408</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.2285</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2331</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3122,25 +3122,29 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.2211</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>0.2285</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3151,25 +3155,25 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.2147</v>
+        <v>0.2211</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3180,49 +3184,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.2077</v>
+        <v>0.2147</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.2066</v>
+        <v>0.2077</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
@@ -3238,54 +3242,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.2056</v>
+        <v>0.2066</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.2051</v>
+        <v>0.2056</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3296,49 +3300,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.2011</v>
+        <v>0.2051</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.1996</v>
+        <v>0.2011</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
@@ -3348,26 +3352,26 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1978</v>
+        <v>0.1996</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
@@ -3377,84 +3381,84 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.1925</v>
+        <v>0.1978</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.1898</v>
+        <v>0.1925</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.1883</v>
+        <v>0.1898</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -3470,49 +3474,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.185</v>
+        <v>0.1883</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.1732</v>
+        <v>0.185</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
@@ -3522,89 +3526,89 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.1704</v>
+        <v>0.1732</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>彰銀</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.1638</v>
+        <v>0.1704</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>彰銀</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.1632</v>
+        <v>0.1638</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3615,20 +3619,20 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.1605</v>
+        <v>0.1632</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
@@ -3644,20 +3648,20 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.1582</v>
+        <v>0.1605</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
@@ -3667,31 +3671,31 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.153</v>
+        <v>0.1582</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3702,54 +3706,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.1514</v>
+        <v>0.153</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.1438</v>
+        <v>0.1514</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3760,112 +3764,112 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.1357</v>
+        <v>0.1438</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.1339</v>
+        <v>0.1357</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.1316</v>
+        <v>0.1339</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.127</v>
+        <v>0.1316</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3876,49 +3880,49 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.1265</v>
+        <v>0.127</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.1262</v>
+        <v>0.1265</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
@@ -3928,26 +3932,26 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.1226</v>
+        <v>0.1262</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
@@ -3957,26 +3961,26 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.1194</v>
+        <v>0.1226</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
@@ -3992,20 +3996,20 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.1181</v>
+        <v>0.1194</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
@@ -4015,60 +4019,60 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.1176</v>
+        <v>0.1181</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.1112</v>
+        <v>0.1176</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4079,25 +4083,25 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>臺企銀</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.1086</v>
+        <v>0.1112</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4108,83 +4112,83 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>臺企銀</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.1001</v>
+        <v>0.1086</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.099</v>
+        <v>0.1001</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.0985</v>
+        <v>0.099</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4195,20 +4199,20 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.0946</v>
+        <v>0.0985</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
@@ -4224,78 +4228,78 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.0944</v>
+        <v>0.0946</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.0851</v>
+        <v>0.0944</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0829</v>
+        <v>0.0851</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
@@ -4305,31 +4309,31 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.0799</v>
+        <v>0.0829</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4340,20 +4344,20 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.0785</v>
+        <v>0.081</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
@@ -4369,86 +4373,144 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.0784</v>
+        <v>0.0799</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0774</v>
+        <v>0.0785</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.0764</v>
+        <v>0.0784</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>110</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>111</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>台中銀</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>金融🏦</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
         </is>
@@ -6606,7 +6668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7239,23 +7301,23 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>漢磊</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>353.1</v>
+        <v>398.6</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7263,11 +7325,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -7286,22 +7348,22 @@
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>2.14</v>
+        <v>-0.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>58.01</v>
+        <v>324.5</v>
       </c>
       <c r="R9" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="S9" t="n">
-        <v>4.14</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>11.8</v>
+        <v>28</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -7311,35 +7373,35 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>303.3</v>
+        <v>353.1</v>
       </c>
       <c r="E10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7354,26 +7416,26 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.68</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>64.42</v>
+        <v>58.01</v>
       </c>
       <c r="R10" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>9.17</v>
+        <v>4.14</v>
       </c>
       <c r="T10" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="U10" t="n">
-        <v>-43.4</v>
+        <v>11.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -7383,35 +7445,35 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>420.8</v>
+        <v>303.3</v>
       </c>
       <c r="E11" t="n">
-        <v>35.5</v>
+        <v>38</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -7423,29 +7485,29 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>6.49</v>
+        <v>0.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>27.01</v>
+        <v>64.42</v>
       </c>
       <c r="R11" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S11" t="n">
-        <v>5.1</v>
+        <v>9.17</v>
       </c>
       <c r="T11" t="n">
-        <v>3.46</v>
+        <v>1.43</v>
       </c>
       <c r="U11" t="n">
-        <v>7.4</v>
+        <v>-43.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -7455,23 +7517,23 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>299.1</v>
+        <v>420.8</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>35.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7479,11 +7541,11 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -7495,31 +7557,103 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>61</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5371</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>31</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q13" t="n">
         <v>127.5</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S13" t="n">
         <v>1.13</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>0.65</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>6.1</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7536,7 +7670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7614,20 +7748,20 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>漢磊</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>398.6</v>
+        <v>396.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -7637,20 +7771,20 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>大國鋼</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>396.6</v>
+        <v>363.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -7660,20 +7794,20 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>大國鋼</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>363.6</v>
+        <v>359.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -7683,20 +7817,20 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>德宏工業</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>359.8</v>
+        <v>354.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7706,20 +7840,20 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>德宏工業</t>
+          <t>中國探針</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>354.7</v>
+        <v>320</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -7729,45 +7863,22 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>中國探針</t>
+          <t>元大期</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>320</v>
       </c>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>56</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>元大期</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>320</v>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>加入 PICKS 抓體檢</t>
         </is>
@@ -10191,7 +10302,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -6668,7 +6668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7373,23 +7373,23 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>353.1</v>
+        <v>354.7</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -7416,26 +7416,26 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>-1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>58.01</v>
+        <v>1054.35</v>
       </c>
       <c r="R10" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="S10" t="n">
-        <v>4.14</v>
+        <v>32.38</v>
       </c>
       <c r="T10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>11.8</v>
+        <v>215</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -7445,35 +7445,35 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>303.3</v>
+        <v>353.1</v>
       </c>
       <c r="E11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -7488,26 +7488,26 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>0.68</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>64.42</v>
+        <v>58.01</v>
       </c>
       <c r="R11" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="S11" t="n">
-        <v>9.17</v>
+        <v>4.14</v>
       </c>
       <c r="T11" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="U11" t="n">
-        <v>-43.4</v>
+        <v>11.8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -7517,35 +7517,35 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>420.8</v>
+        <v>303.3</v>
       </c>
       <c r="E12" t="n">
-        <v>35.5</v>
+        <v>38</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -7557,29 +7557,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>6.49</v>
+        <v>0.68</v>
       </c>
       <c r="Q12" t="n">
-        <v>27.01</v>
+        <v>64.42</v>
       </c>
       <c r="R12" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S12" t="n">
-        <v>5.1</v>
+        <v>9.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.46</v>
+        <v>1.43</v>
       </c>
       <c r="U12" t="n">
-        <v>7.4</v>
+        <v>-43.4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -7589,23 +7589,23 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>299.1</v>
+        <v>420.8</v>
       </c>
       <c r="E13" t="n">
-        <v>31</v>
+        <v>35.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7613,11 +7613,11 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -7629,31 +7629,103 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>61</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>59</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5371</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>31</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q14" t="n">
         <v>127.5</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>100</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>1.13</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>0.65</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>6.1</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7670,7 +7742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7817,20 +7889,20 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>德宏工業</t>
+          <t>中國探針</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>354.7</v>
+        <v>320</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7840,45 +7912,22 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>中國探針</t>
+          <t>元大期</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>320</v>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>56</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>元大期</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>320</v>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>加入 PICKS 抓體檢</t>
         </is>

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -1355,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3851,20 +3851,20 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.1316</v>
+        <v>0.1331</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
@@ -3880,49 +3880,49 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.127</v>
+        <v>0.1329</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.1265</v>
+        <v>0.1316</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
@@ -3932,55 +3932,55 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.1262</v>
+        <v>0.127</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.1226</v>
+        <v>0.1265</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
@@ -3990,26 +3990,26 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.1194</v>
+        <v>0.1265</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
@@ -4019,26 +4019,26 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.1181</v>
+        <v>0.1262</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
@@ -4048,31 +4048,31 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.1176</v>
+        <v>0.1226</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4083,20 +4083,20 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.1112</v>
+        <v>0.1194</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
@@ -4112,83 +4112,83 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>臺企銀</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.1086</v>
+        <v>0.1181</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.1001</v>
+        <v>0.1176</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.099</v>
+        <v>0.1112</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4199,25 +4199,25 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>臺企銀</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.0985</v>
+        <v>0.1086</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4228,25 +4228,25 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.0946</v>
+        <v>0.1061</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4257,54 +4257,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.0944</v>
+        <v>0.1001</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0851</v>
+        <v>0.099</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4315,20 +4315,20 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.0829</v>
+        <v>0.0985</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
@@ -4338,26 +4338,26 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.081</v>
+        <v>0.0946</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
@@ -4367,31 +4367,31 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.0799</v>
+        <v>0.0944</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4402,20 +4402,20 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0785</v>
+        <v>0.0851</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
@@ -4425,92 +4425,208 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.0784</v>
+        <v>0.0829</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.0774</v>
+        <v>0.081</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0764</v>
+        <v>0.0799</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>108</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>可成</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>109</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>士電</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>110</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>111</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>台中銀</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
           <t>金融🏦</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
         </is>
@@ -6668,7 +6784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7011,23 +7127,23 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>313.4</v>
+        <v>490.2</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -7035,11 +7151,11 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -7054,26 +7170,26 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>35.84</v>
+        <v>73.8</v>
       </c>
       <c r="R5" t="n">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="S5" t="n">
-        <v>3.82</v>
+        <v>5.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.05</v>
+        <v>0.65</v>
       </c>
       <c r="U5" t="n">
-        <v>37</v>
+        <v>25.6</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -7083,31 +7199,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>343.1</v>
+        <v>313.4</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -7126,26 +7242,26 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.19</v>
+        <v>35.84</v>
       </c>
       <c r="R6" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>3.82</v>
       </c>
       <c r="T6" t="n">
-        <v>4.43</v>
+        <v>1.05</v>
       </c>
       <c r="U6" t="n">
-        <v>10.3</v>
+        <v>37</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7155,51 +7271,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>486.4</v>
+        <v>343.1</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="K7" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8.6</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -7208,44 +7318,48 @@
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>89.70999999999999</v>
+        <v>20.19</v>
       </c>
       <c r="R7" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="S7" t="n">
-        <v>15.26</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.43</v>
       </c>
       <c r="U7" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
+        <v>10.3</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>臺慶科</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>362.1</v>
+        <v>486.4</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7253,7 +7367,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -7262,12 +7376,18 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="K8" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.6</v>
+      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -7276,60 +7396,56 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>0.76</v>
+        <v>1.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.8</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>15.26</v>
       </c>
       <c r="T8" t="n">
-        <v>1.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>55</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>中探針</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>320</v>
+      </c>
+      <c r="E9" t="n">
+        <v>54</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>47</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3707</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>漢磊</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>398.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>47</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -7348,22 +7464,22 @@
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>-0.29</v>
+        <v>2.27</v>
       </c>
       <c r="Q9" t="n">
-        <v>324.5</v>
+        <v>159.6</v>
       </c>
       <c r="R9" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>9.69</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>28</v>
+        <v>51.2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -7373,31 +7489,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>50</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3357</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>臺慶科</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="E10" t="n">
         <v>52</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>5475</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>德宏</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>354.7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>44</v>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -7420,22 +7536,22 @@
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>-1.5</v>
+        <v>0.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>1054.35</v>
+        <v>29.8</v>
       </c>
       <c r="R10" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>32.38</v>
+        <v>3.65</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>215</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -7445,103 +7561,99 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>元大期</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>353.1</v>
+        <v>320</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>45</v>
-      </c>
+          <t>金融🏦</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>0.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>58.01</v>
+        <v>11.62</v>
       </c>
       <c r="R11" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="S11" t="n">
-        <v>4.14</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>1.51</v>
+        <v>5.53</v>
       </c>
       <c r="U11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>80.40000000000001</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>漢磊</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>303.3</v>
+        <v>398.6</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -7560,26 +7672,26 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>0.68</v>
+        <v>-0.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>64.42</v>
+        <v>324.5</v>
       </c>
       <c r="R12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="S12" t="n">
-        <v>9.17</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-43.4</v>
+        <v>28</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -7589,23 +7701,23 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>420.8</v>
+        <v>354.7</v>
       </c>
       <c r="E13" t="n">
-        <v>35.5</v>
+        <v>44</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7613,11 +7725,11 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -7629,29 +7741,29 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>6.49</v>
+        <v>-1.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>27.01</v>
+        <v>1054.35</v>
       </c>
       <c r="R13" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1</v>
+        <v>32.38</v>
       </c>
       <c r="T13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>7.4</v>
+        <v>215</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -7661,23 +7773,23 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>299.1</v>
+        <v>353.1</v>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7685,11 +7797,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -7704,28 +7816,244 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>3.75</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>127.5</v>
+        <v>58.01</v>
       </c>
       <c r="R14" t="n">
         <v>100</v>
       </c>
       <c r="S14" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>58</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>303.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>38</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>69</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="R15" t="n">
+        <v>71</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>45</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5903</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>420.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>39</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>-15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="R16" t="n">
+        <v>61</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>59</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5371</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>24</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>100</v>
+      </c>
+      <c r="S17" t="n">
         <v>1.13</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T17" t="n">
         <v>0.65</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U17" t="n">
         <v>6.1</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
@@ -7742,7 +8070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7774,20 +8102,20 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>信昌電陶</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>490.2</v>
+        <v>460.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -7797,20 +8125,20 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>460.3</v>
+        <v>396.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -7820,20 +8148,20 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>大國鋼</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>396.6</v>
+        <v>363.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -7843,91 +8171,22 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>大國鋼</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>363.6</v>
+        <v>359.8</v>
       </c>
       <c r="E5" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>51</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>8932</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>智通*</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>359.8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6217</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>中國探針</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>320</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>加入 PICKS 抓體檢</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>元大期</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>320</v>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>加入 PICKS 抓體檢</t>
         </is>
@@ -10351,7 +10610,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">

--- a/data/台股_0050納入預測.xlsx
+++ b/data/台股_0050納入預測.xlsx
@@ -1355,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1991,20 +1991,20 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.5463</v>
+        <v>0.6958</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2013,31 +2013,31 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.535</v>
+        <v>0.5463</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2057,20 +2057,20 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.4889</v>
+        <v>0.535</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2090,20 +2090,20 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.4634</v>
+        <v>0.4889</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2123,20 +2123,20 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.4303</v>
+        <v>0.4634</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2156,20 +2156,20 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.408</v>
+        <v>0.4303</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2189,20 +2189,20 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.3992</v>
+        <v>0.408</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2222,20 +2222,20 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.3887</v>
+        <v>0.3992</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2255,20 +2255,20 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.3791</v>
+        <v>0.3887</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2288,20 +2288,20 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.3768</v>
+        <v>0.3791</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2321,20 +2321,20 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.3736</v>
+        <v>0.3768</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2354,20 +2354,20 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.3577</v>
+        <v>0.3736</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2387,20 +2387,20 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.3466</v>
+        <v>0.3577</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2409,31 +2409,31 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3442</v>
+        <v>0.3466</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2442,31 +2442,31 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.3367</v>
+        <v>0.3442</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2475,31 +2475,31 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.3319</v>
+        <v>0.3367</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2508,31 +2508,31 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.3226</v>
+        <v>0.3319</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2552,20 +2552,20 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.3171</v>
+        <v>0.3226</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2574,31 +2574,31 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2989</v>
+        <v>0.3171</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2607,31 +2607,31 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.2947</v>
+        <v>0.2989</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2651,20 +2651,20 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.2919</v>
+        <v>0.2947</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2684,20 +2684,20 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.2854</v>
+        <v>0.2919</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2706,31 +2706,31 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.2805</v>
+        <v>0.2854</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2750,22 +2750,26 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.2802</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>0.2805</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>D</t>
@@ -2773,35 +2777,31 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2797</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2802</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2812,20 +2812,20 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2762</v>
+        <v>0.2797</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2845,20 +2845,20 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.2714</v>
+        <v>0.2762</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2878,25 +2878,29 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.2641</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
+        <v>0.2714</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2907,29 +2911,25 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.2626</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2641</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2940,25 +2940,29 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.2577</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
+        <v>0.2626</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2969,25 +2973,25 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.251</v>
+        <v>0.2577</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2998,91 +3002,87 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.2464</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.251</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.2429</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
+        <v>0.2464</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2429</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3093,58 +3093,58 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.2331</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>0.2408</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.2285</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>0.2331</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3155,25 +3155,29 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.2211</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
+        <v>0.2285</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3184,25 +3188,25 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.2147</v>
+        <v>0.2211</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3213,49 +3217,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.2077</v>
+        <v>0.2147</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.2066</v>
+        <v>0.2077</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
@@ -3271,54 +3275,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.2056</v>
+        <v>0.2066</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.2051</v>
+        <v>0.2056</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3329,49 +3333,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.2011</v>
+        <v>0.2051</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1996</v>
+        <v>0.2011</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
@@ -3381,26 +3385,26 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.1978</v>
+        <v>0.1996</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -3410,84 +3414,84 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.1925</v>
+        <v>0.1978</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.1898</v>
+        <v>0.1925</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.1883</v>
+        <v>0.1898</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
@@ -3503,49 +3507,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.185</v>
+        <v>0.1883</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.1732</v>
+        <v>0.185</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
@@ -3555,89 +3559,89 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.1704</v>
+        <v>0.1732</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>彰銀</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.1638</v>
+        <v>0.1704</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>彰銀</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.1632</v>
+        <v>0.1638</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3648,20 +3652,20 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.1605</v>
+        <v>0.1632</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
@@ -3677,20 +3681,20 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.1582</v>
+        <v>0.1605</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
@@ -3700,31 +3704,31 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.153</v>
+        <v>0.1582</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3735,54 +3739,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.1514</v>
+        <v>0.153</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.1438</v>
+        <v>0.1514</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3793,170 +3797,170 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.1357</v>
+        <v>0.1438</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.1339</v>
+        <v>0.1357</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.1331</v>
+        <v>0.1339</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.1329</v>
+        <v>0.1331</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.1316</v>
+        <v>0.1329</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.127</v>
+        <v>0.1316</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3967,45 +3971,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.1265</v>
+        <v>0.127</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -4019,26 +4023,26 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.1262</v>
+        <v>0.1265</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
@@ -4048,26 +4052,26 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.1226</v>
+        <v>0.1262</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
@@ -4077,26 +4081,26 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.1194</v>
+        <v>0.1226</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
@@ -4112,20 +4116,20 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.1181</v>
+        <v>0.1194</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
@@ -4135,60 +4139,60 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.1176</v>
+        <v>0.1181</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.1112</v>
+        <v>0.1176</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4199,25 +4203,25 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>臺企銀</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.1086</v>
+        <v>0.1112</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>金融🏦</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4228,25 +4232,25 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>臺企銀</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.1061</v>
+        <v>0.1086</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>金融🏦</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4257,83 +4261,83 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.1001</v>
+        <v>0.1061</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.099</v>
+        <v>0.1001</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.0985</v>
+        <v>0.099</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4344,20 +4348,20 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.0946</v>
+        <v>0.0985</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
@@ -4373,78 +4377,78 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.0944</v>
+        <v>0.0946</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.0851</v>
+        <v>0.0944</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.0829</v>
+        <v>0.0851</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
@@ -4454,26 +4458,26 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.081</v>
+        <v>0.0829</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
@@ -4483,118 +4487,118 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0799</v>
+        <v>0.081</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.0785</v>
+        <v>0.0799</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.0784</v>
+        <v>0.0785</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.0774</v>
+        <v>0.0784</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4605,28 +4609,57 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.0764</v>
+        <v>0.0774</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>111</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>台中銀</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>金融🏦</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
         </is>
@@ -10610,7 +10643,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6">
